--- a/PIP_장부.xlsx
+++ b/PIP_장부.xlsx
@@ -5,11 +5,11 @@
   <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ckswl\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ckswl\Desktop\PIP\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="22812" windowHeight="8094" tabRatio="500"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="25380" windowHeight="11100" tabRatio="500"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="1" sheetId="1" r:id="rId4"/>
@@ -30,9 +30,57 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="19">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="24">
+  <x:si>
+    <x:t>UI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>enemy</x:t>
+  </x:si>
+  <x:si>
+    <x:t>지원금</x:t>
+  </x:si>
+  <x:si>
+    <x:t>잔액</x:t>
+  </x:si>
+  <x:si>
+    <x:t>내역</x:t>
+  </x:si>
+  <x:si>
+    <x:t>남은돈</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그 외</x:t>
+  </x:si>
+  <x:si>
+    <x:t>합계</x:t>
+  </x:si>
+  <x:si>
+    <x:t>월/일</x:t>
+  </x:si>
+  <x:si>
+    <x:t>교통비</x:t>
+  </x:si>
+  <x:si>
+    <x:t>지출액</x:t>
+  </x:si>
+  <x:si>
+    <x:t>식비</x:t>
+  </x:si>
+  <x:si>
+    <x:t>생활비</x:t>
+  </x:si>
+  <x:si>
+    <x:t>예산</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ddr5 램 x2</x:t>
+  </x:si>
   <x:si>
     <x:t>변동지출: 소비성 지출(구독료도 포함!)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>교육/문화비</x:t>
   </x:si>
   <x:si>
     <x:t>총 지출</x:t>
@@ -41,52 +89,19 @@
     <x:t>남은 예산</x:t>
   </x:si>
   <x:si>
-    <x:t>교육/문화비</x:t>
+    <x:t>npc bundle</x:t>
   </x:si>
   <x:si>
-    <x:t>총 자산</x:t>
+    <x:t>FIELD</x:t>
   </x:si>
   <x:si>
-    <x:t>지원금</x:t>
+    <x:t>enemy bundle</x:t>
   </x:si>
   <x:si>
-    <x:t>식비</x:t>
+    <x:t>TREE</x:t>
   </x:si>
   <x:si>
-    <x:t>잔액</x:t>
-  </x:si>
-  <x:si>
-    <x:t>생활비</x:t>
-  </x:si>
-  <x:si>
-    <x:t>남은돈</x:t>
-  </x:si>
-  <x:si>
-    <x:t>월/일</x:t>
-  </x:si>
-  <x:si>
-    <x:t>내역</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그 외</x:t>
-  </x:si>
-  <x:si>
-    <x:t>지출액</x:t>
-  </x:si>
-  <x:si>
-    <x:t>예산</x:t>
-  </x:si>
-  <x:si>
-    <x:t>합계</x:t>
-  </x:si>
-  <x:si>
-    <x:t>교통비</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ddr5 램 x2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>에셋1</x:t>
+    <x:t>weapon pack</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -126,6 +141,11 @@
     <x:font>
       <x:name val="Arial"/>
       <x:sz val="10"/>
+      <x:color rgb="ff000000"/>
+    </x:font>
+    <x:font>
+      <x:name val="맑은 고딕"/>
+      <x:sz val="11"/>
       <x:color rgb="ff000000"/>
     </x:font>
     <x:font>
@@ -188,26 +208,6 @@
           <x:name val="Arial"/>
           <x:sz val="10"/>
           <x:color rgb="ffff0000"/>
-        </x:font>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:font hs:extension="1">
-          <x:name val="Arial"/>
-          <x:sz val="12"/>
-          <x:color rgb="ff000000"/>
-          <hs:size val="100"/>
-          <hs:ratio val="100"/>
-          <hs:spacing val="0"/>
-          <hs:offset val="0"/>
-        </x:font>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:font>
-          <x:name val="Arial"/>
-          <x:sz val="12"/>
-          <x:color rgb="ff000000"/>
         </x:font>
       </mc:Fallback>
     </mc:AlternateContent>
@@ -295,13 +295,28 @@
         </x:font>
       </mc:Fallback>
     </mc:AlternateContent>
-    <x:font>
-      <x:name val="맑은 고딕"/>
-      <x:sz val="11"/>
-      <x:color rgb="ff000000"/>
-    </x:font>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:font hs:extension="1">
+          <x:name val="Arial"/>
+          <x:sz val="12"/>
+          <x:color rgb="ff000000"/>
+          <hs:size val="100"/>
+          <hs:ratio val="100"/>
+          <hs:spacing val="0"/>
+          <hs:offset val="0"/>
+        </x:font>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:font>
+          <x:name val="Arial"/>
+          <x:sz val="12"/>
+          <x:color rgb="ff000000"/>
+        </x:font>
+      </mc:Fallback>
+    </mc:AlternateContent>
   </x:fonts>
-  <x:fills count="10">
+  <x:fills count="8">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -322,18 +337,6 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="ff9be5c8"/>
-        <x:bgColor rgb="fffbe5d7"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="ffffff00"/>
-        <x:bgColor rgb="ffffff00"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
         <x:fgColor rgb="fffff2cc"/>
         <x:bgColor rgb="fffff2cc"/>
       </x:patternFill>
@@ -346,14 +349,14 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="ff9be5c8"/>
-        <x:bgColor indexed="64"/>
+        <x:fgColor rgb="ffe2f0d9"/>
+        <x:bgColor rgb="ffe2f0d9"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="ffe2f0d9"/>
-        <x:bgColor rgb="ffe2f0d9"/>
+        <x:fgColor rgb="ffffff00"/>
+        <x:bgColor rgb="ffffff00"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -545,43 +548,17 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="17" fillId="0" borderId="0">
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="39">
+  <x:cellXfs count="36">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
     <x:xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
-          <x:alignment horizontal="center" vertical="center"/>
-          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
-        </x:xf>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-          <x:alignment horizontal="center" vertical="center"/>
-        </x:xf>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
-          <x:alignment horizontal="center" vertical="center"/>
-          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
-        </x:xf>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-          <x:alignment horizontal="center" vertical="center"/>
-        </x:xf>
-      </mc:Fallback>
-    </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
         <x:xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
@@ -595,96 +572,83 @@
         </x:xf>
       </mc:Fallback>
     </mc:AlternateContent>
-    <x:xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <x:alignment horizontal="general" vertical="center"/>
-    </x:xf>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
+        <x:xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
           <x:alignment horizontal="center" vertical="center"/>
           <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
         </x:xf>
       </mc:Choice>
       <mc:Fallback>
-        <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+        <x:xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
           <x:alignment horizontal="center" vertical="center"/>
         </x:xf>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
+        <x:xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
           <x:alignment horizontal="center" vertical="center"/>
           <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
         </x:xf>
       </mc:Choice>
       <mc:Fallback>
-        <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+        <x:xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+          <x:alignment horizontal="center" vertical="center"/>
+        </x:xf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
+          <x:alignment horizontal="center" vertical="center"/>
+          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
+        </x:xf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
           <x:alignment horizontal="center" vertical="center"/>
         </x:xf>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:xf numFmtId="164" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
+        <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
           <x:alignment horizontal="center" vertical="center"/>
           <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
         </x:xf>
       </mc:Choice>
       <mc:Fallback>
-        <x:xf numFmtId="164" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+        <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
           <x:alignment horizontal="center" vertical="center"/>
         </x:xf>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
+        <x:xf numFmtId="164" fontId="10" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
           <x:alignment horizontal="center" vertical="center"/>
           <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
         </x:xf>
       </mc:Choice>
       <mc:Fallback>
-        <x:xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+        <x:xf numFmtId="164" fontId="10" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
           <x:alignment horizontal="center" vertical="center"/>
         </x:xf>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" hs:applyExtension="1">
+        <x:xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
           <x:alignment horizontal="center" vertical="center"/>
           <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
         </x:xf>
       </mc:Choice>
       <mc:Fallback>
-        <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-          <x:alignment horizontal="center" vertical="center"/>
-        </x:xf>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:xf numFmtId="164" fontId="9" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
-          <x:alignment horizontal="center" vertical="center"/>
-          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
-        </x:xf>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:xf numFmtId="164" fontId="9" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-          <x:alignment horizontal="center" vertical="center"/>
-        </x:xf>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:xf numFmtId="165" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
-          <x:alignment horizontal="center" vertical="center"/>
-          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
-        </x:xf>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:xf numFmtId="165" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+        <x:xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
           <x:alignment horizontal="center" vertical="center"/>
         </x:xf>
       </mc:Fallback>
@@ -704,29 +668,68 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:xf numFmtId="164" fontId="9" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
+        <x:xf numFmtId="164" fontId="10" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
           <x:alignment horizontal="center" vertical="center"/>
           <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
         </x:xf>
       </mc:Choice>
       <mc:Fallback>
-        <x:xf numFmtId="164" fontId="9" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+        <x:xf numFmtId="164" fontId="10" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
           <x:alignment horizontal="center" vertical="center"/>
         </x:xf>
       </mc:Fallback>
     </mc:AlternateContent>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <x:alignment horizontal="general" vertical="bottom"/>
-    </x:xf>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
+        <x:xf numFmtId="165" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
           <x:alignment horizontal="center" vertical="center"/>
           <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
         </x:xf>
       </mc:Choice>
       <mc:Fallback>
-        <x:xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+        <x:xf numFmtId="165" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+          <x:alignment horizontal="center" vertical="center"/>
+        </x:xf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" hs:applyExtension="1">
+          <x:alignment horizontal="center" vertical="center"/>
+          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
+        </x:xf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+          <x:alignment horizontal="center" vertical="center"/>
+        </x:xf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:xf numFmtId="164" fontId="10" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
+          <x:alignment horizontal="center" vertical="center"/>
+          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
+        </x:xf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:xf numFmtId="164" fontId="10" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+          <x:alignment horizontal="center" vertical="center"/>
+        </x:xf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom"/>
+    </x:xf>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
+          <x:alignment horizontal="center" vertical="center"/>
+          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
+        </x:xf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
           <x:alignment horizontal="center" vertical="center"/>
         </x:xf>
       </mc:Fallback>
@@ -734,28 +737,31 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom"/>
+    </x:xf>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
+        <x:xf numFmtId="58" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
           <x:alignment horizontal="center" vertical="center"/>
           <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
         </x:xf>
       </mc:Choice>
       <mc:Fallback>
-        <x:xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+        <x:xf numFmtId="58" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
           <x:alignment horizontal="center" vertical="center"/>
         </x:xf>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:xf numFmtId="0" fontId="12" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
+        <x:xf numFmtId="164" fontId="7" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
           <x:alignment horizontal="center" vertical="center"/>
           <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
         </x:xf>
       </mc:Choice>
       <mc:Fallback>
-        <x:xf numFmtId="0" fontId="12" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+        <x:xf numFmtId="164" fontId="7" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
           <x:alignment horizontal="center" vertical="center"/>
         </x:xf>
       </mc:Fallback>
@@ -763,19 +769,6 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:xf numFmtId="164" fontId="6" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
-          <x:alignment horizontal="center" vertical="center"/>
-          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
-        </x:xf>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:xf numFmtId="164" fontId="6" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-          <x:alignment horizontal="center" vertical="center"/>
-        </x:xf>
-      </mc:Fallback>
-    </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
         <x:xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
@@ -794,13 +787,13 @@
     </x:xf>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:xf numFmtId="164" fontId="14" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
+        <x:xf numFmtId="164" fontId="14" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
           <x:alignment horizontal="center" vertical="center"/>
           <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
         </x:xf>
       </mc:Choice>
       <mc:Fallback>
-        <x:xf numFmtId="164" fontId="14" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+        <x:xf numFmtId="164" fontId="14" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
           <x:alignment horizontal="center" vertical="center"/>
         </x:xf>
       </mc:Fallback>
@@ -814,54 +807,48 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="general" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="general" vertical="bottom"/>
-    </x:xf>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:xf numFmtId="164" fontId="9" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
+        <x:xf numFmtId="164" fontId="10" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
           <x:alignment horizontal="center" vertical="center"/>
           <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
         </x:xf>
       </mc:Choice>
       <mc:Fallback>
-        <x:xf numFmtId="164" fontId="9" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-          <x:alignment horizontal="center" vertical="center"/>
-        </x:xf>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="general" vertical="bottom"/>
-    </x:xf>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:xf numFmtId="164" fontId="15" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
-          <x:alignment horizontal="center" vertical="center"/>
-          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
-        </x:xf>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:xf numFmtId="164" fontId="15" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+        <x:xf numFmtId="164" fontId="10" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
           <x:alignment horizontal="center" vertical="center"/>
         </x:xf>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:xf numFmtId="0" fontId="6" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
+        <x:xf numFmtId="164" fontId="15" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
           <x:alignment horizontal="center" vertical="center"/>
           <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
         </x:xf>
       </mc:Choice>
       <mc:Fallback>
-        <x:xf numFmtId="0" fontId="6" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+        <x:xf numFmtId="164" fontId="15" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
           <x:alignment horizontal="center" vertical="center"/>
         </x:xf>
       </mc:Fallback>
     </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:xf numFmtId="0" fontId="7" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
+          <x:alignment horizontal="center" vertical="center"/>
+          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
+        </x:xf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:xf numFmtId="0" fontId="7" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+          <x:alignment horizontal="center" vertical="center"/>
+        </x:xf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom"/>
+    </x:xf>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
         <x:xf numFmtId="164" fontId="16" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
@@ -877,50 +864,37 @@
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:xf numFmtId="164" fontId="16" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
+        <x:xf numFmtId="164" fontId="16" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
           <x:alignment horizontal="center" vertical="center"/>
           <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
         </x:xf>
       </mc:Choice>
       <mc:Fallback>
-        <x:xf numFmtId="164" fontId="16" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+        <x:xf numFmtId="164" fontId="16" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
           <x:alignment horizontal="center" vertical="center"/>
         </x:xf>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:xf numFmtId="164" fontId="16" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
+        <x:xf numFmtId="0" fontId="17" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
           <x:alignment horizontal="center" vertical="center"/>
           <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
         </x:xf>
       </mc:Choice>
       <mc:Fallback>
-        <x:xf numFmtId="164" fontId="16" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+        <x:xf numFmtId="0" fontId="17" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
           <x:alignment horizontal="center" vertical="center"/>
         </x:xf>
       </mc:Fallback>
     </mc:AlternateContent>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:xf numFmtId="58" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
-          <x:alignment horizontal="center" vertical="center"/>
-          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
-        </x:xf>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:xf numFmtId="58" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-          <x:alignment horizontal="center" vertical="center"/>
-        </x:xf>
-      </mc:Fallback>
-    </mc:AlternateContent>
   </x:cellXfs>
   <x:cellStyles count="2">
     <x:cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <x:cellStyle name="표준" xfId="1" builtinId="0" iLevel="0"/>
+    <x:cellStyle name="표준" xfId="1"/>
   </x:cellStyles>
   <x:dxfs/>
   <x:tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1144,27 +1118,27 @@
   <x:sheetData>
     <x:row r="1" spans="2:4" ht="25.5" customHeight="1">
       <x:c r="B1" s="2" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C1" s="21">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C1" s="20">
         <x:v>1000000</x:v>
       </x:c>
-      <x:c r="D1" s="20"/>
+      <x:c r="D1" s="21"/>
     </x:row>
     <x:row r="2" spans="2:9" ht="25.5" customHeight="1">
       <x:c r="B2" s="22" t="s">
-        <x:v>7</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C2" s="24">
         <x:f>SUM(C1:D1,-C29:D29)</x:f>
-        <x:v>576980</x:v>
+        <x:v>1000000</x:v>
       </x:c>
       <x:c r="D2" s="25"/>
-      <x:c r="E2" s="37"/>
-      <x:c r="F2" s="37"/>
-      <x:c r="G2" s="37"/>
-      <x:c r="H2" s="37"/>
-      <x:c r="I2" s="37"/>
+      <x:c r="E2" s="18"/>
+      <x:c r="F2" s="18"/>
+      <x:c r="G2" s="18"/>
+      <x:c r="H2" s="18"/>
+      <x:c r="I2" s="18"/>
     </x:row>
     <x:row r="3" spans="2:4" ht="10.5" customHeight="1">
       <x:c r="B3" s="23"/>
@@ -1176,356 +1150,392 @@
     </x:row>
     <x:row r="5" spans="2:16" ht="25.5" customHeight="1">
       <x:c r="B5" s="2" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C5" s="30">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C5" s="28">
         <x:f>C1</x:f>
         <x:v>1000000</x:v>
       </x:c>
-      <x:c r="D5" s="20"/>
-      <x:c r="E5" s="37"/>
-      <x:c r="F5" s="37"/>
-      <x:c r="G5" s="37"/>
-      <x:c r="H5" s="37"/>
-      <x:c r="I5" s="37"/>
-      <x:c r="J5" s="37"/>
-      <x:c r="K5" s="37"/>
-      <x:c r="L5" s="37"/>
-      <x:c r="M5" s="37"/>
-      <x:c r="N5" s="37"/>
-      <x:c r="O5" s="37"/>
-      <x:c r="P5" s="37"/>
+      <x:c r="D5" s="21"/>
+      <x:c r="E5" s="18"/>
+      <x:c r="F5" s="18"/>
+      <x:c r="G5" s="18"/>
+      <x:c r="H5" s="18"/>
+      <x:c r="I5" s="18"/>
+      <x:c r="J5" s="18"/>
+      <x:c r="K5" s="18"/>
+      <x:c r="L5" s="18"/>
+      <x:c r="M5" s="18"/>
+      <x:c r="N5" s="18"/>
+      <x:c r="O5" s="18"/>
+      <x:c r="P5" s="18"/>
     </x:row>
     <x:row r="6" spans="2:16" ht="25.5" customHeight="1">
       <x:c r="B6" s="2" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C6" s="32">
-        <x:f>C2</x:f>
-        <x:v>576980</x:v>
-      </x:c>
-      <x:c r="D6" s="20"/>
-      <x:c r="E6" s="37"/>
-      <x:c r="F6" s="37"/>
-      <x:c r="G6" s="37"/>
-      <x:c r="H6" s="37"/>
-      <x:c r="I6" s="37"/>
-      <x:c r="J6" s="37"/>
-      <x:c r="K6" s="37"/>
-      <x:c r="L6" s="37"/>
-      <x:c r="M6" s="37"/>
-      <x:c r="N6" s="37"/>
-      <x:c r="O6" s="37"/>
-      <x:c r="P6" s="37"/>
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C6" s="29">
+        <x:f>C2-SUM(D9:D23)</x:f>
+        <x:v>59690</x:v>
+      </x:c>
+      <x:c r="D6" s="21"/>
+      <x:c r="E6" s="18"/>
+      <x:c r="F6" s="18"/>
+      <x:c r="G6" s="18"/>
+      <x:c r="H6" s="18"/>
+      <x:c r="I6" s="18"/>
+      <x:c r="J6" s="18"/>
+      <x:c r="K6" s="18"/>
+      <x:c r="L6" s="18"/>
+      <x:c r="M6" s="18"/>
+      <x:c r="N6" s="18"/>
+      <x:c r="O6" s="18"/>
+      <x:c r="P6" s="18"/>
     </x:row>
     <x:row r="7" spans="2:16" ht="25.5" customHeight="1">
-      <x:c r="B7" s="33" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C7" s="29"/>
-      <x:c r="D7" s="20"/>
-      <x:c r="E7" s="37"/>
-      <x:c r="F7" s="37"/>
-      <x:c r="G7" s="37"/>
-      <x:c r="H7" s="37"/>
-      <x:c r="I7" s="37"/>
-      <x:c r="J7" s="37"/>
-      <x:c r="K7" s="37"/>
-      <x:c r="L7" s="37"/>
-      <x:c r="M7" s="37"/>
-      <x:c r="N7" s="37"/>
-      <x:c r="O7" s="37"/>
-      <x:c r="P7" s="37"/>
+      <x:c r="B7" s="30" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C7" s="31"/>
+      <x:c r="D7" s="21"/>
+      <x:c r="E7" s="18"/>
+      <x:c r="F7" s="18"/>
+      <x:c r="G7" s="18"/>
+      <x:c r="H7" s="18"/>
+      <x:c r="I7" s="18"/>
+      <x:c r="J7" s="18"/>
+      <x:c r="K7" s="18"/>
+      <x:c r="L7" s="18"/>
+      <x:c r="M7" s="18"/>
+      <x:c r="N7" s="18"/>
+      <x:c r="O7" s="18"/>
+      <x:c r="P7" s="18"/>
     </x:row>
     <x:row r="8" spans="2:16" ht="25.5" customHeight="1">
       <x:c r="B8" s="6" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C8" s="7" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D8" s="8" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C8" s="7" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D8" s="8" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E8" s="37"/>
-      <x:c r="F8" s="37"/>
-      <x:c r="G8" s="37"/>
-      <x:c r="H8" s="37"/>
-      <x:c r="I8" s="37"/>
-      <x:c r="J8" s="37"/>
-      <x:c r="K8" s="37"/>
-      <x:c r="L8" s="37"/>
-      <x:c r="M8" s="37"/>
-      <x:c r="N8" s="37"/>
-      <x:c r="O8" s="37"/>
-      <x:c r="P8" s="37"/>
+      <x:c r="E8" s="18"/>
+      <x:c r="F8" s="18"/>
+      <x:c r="G8" s="18"/>
+      <x:c r="H8" s="18"/>
+      <x:c r="I8" s="18"/>
+      <x:c r="J8" s="18"/>
+      <x:c r="K8" s="18"/>
+      <x:c r="L8" s="18"/>
+      <x:c r="M8" s="18"/>
+      <x:c r="N8" s="18"/>
+      <x:c r="O8" s="18"/>
+      <x:c r="P8" s="18"/>
     </x:row>
     <x:row r="9" spans="2:16" ht="25.5" customHeight="1">
-      <x:c r="B9" s="38">
+      <x:c r="B9" s="19">
         <x:v>45999</x:v>
       </x:c>
       <x:c r="C9" s="10" t="s">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D9" s="11">
         <x:v>401000</x:v>
       </x:c>
-      <x:c r="E9" s="37"/>
-      <x:c r="F9" s="37"/>
-      <x:c r="G9" s="37"/>
-      <x:c r="H9" s="37"/>
-      <x:c r="I9" s="37"/>
-      <x:c r="J9" s="37"/>
-      <x:c r="K9" s="37"/>
-      <x:c r="L9" s="37"/>
-      <x:c r="M9" s="37"/>
-      <x:c r="N9" s="37"/>
-      <x:c r="O9" s="37"/>
-      <x:c r="P9" s="37"/>
+      <x:c r="E9" s="18"/>
+      <x:c r="F9" s="18"/>
+      <x:c r="G9" s="18"/>
+      <x:c r="H9" s="18"/>
+      <x:c r="I9" s="18"/>
+      <x:c r="J9" s="18"/>
+      <x:c r="K9" s="18"/>
+      <x:c r="L9" s="18"/>
+      <x:c r="M9" s="18"/>
+      <x:c r="N9" s="18"/>
+      <x:c r="O9" s="18"/>
+      <x:c r="P9" s="18"/>
     </x:row>
     <x:row r="10" spans="2:16" ht="25.5" customHeight="1">
-      <x:c r="B10" s="38">
+      <x:c r="B10" s="19">
         <x:v>46001</x:v>
       </x:c>
       <x:c r="C10" s="10" t="s">
-        <x:v>18</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D10" s="14">
         <x:v>22020</x:v>
       </x:c>
-      <x:c r="E10" s="37"/>
-      <x:c r="F10" s="37"/>
-      <x:c r="G10" s="37"/>
-      <x:c r="H10" s="37"/>
-      <x:c r="I10" s="37"/>
-      <x:c r="J10" s="37"/>
-      <x:c r="K10" s="37"/>
-      <x:c r="L10" s="37"/>
-      <x:c r="M10" s="37"/>
-      <x:c r="N10" s="37"/>
-      <x:c r="O10" s="37"/>
-      <x:c r="P10" s="37"/>
+      <x:c r="E10" s="18"/>
+      <x:c r="F10" s="18"/>
+      <x:c r="G10" s="18"/>
+      <x:c r="H10" s="18"/>
+      <x:c r="I10" s="18"/>
+      <x:c r="J10" s="18"/>
+      <x:c r="K10" s="18"/>
+      <x:c r="L10" s="18"/>
+      <x:c r="M10" s="18"/>
+      <x:c r="N10" s="18"/>
+      <x:c r="O10" s="18"/>
+      <x:c r="P10" s="18"/>
     </x:row>
     <x:row r="11" spans="2:16" ht="25.5" customHeight="1">
-      <x:c r="B11" s="9"/>
-      <x:c r="C11" s="10"/>
-      <x:c r="D11" s="14"/>
-      <x:c r="E11" s="37"/>
-      <x:c r="F11" s="37"/>
-      <x:c r="G11" s="37"/>
-      <x:c r="H11" s="37"/>
-      <x:c r="I11" s="37"/>
-      <x:c r="J11" s="37"/>
-      <x:c r="K11" s="37"/>
-      <x:c r="L11" s="37"/>
-      <x:c r="M11" s="37"/>
-      <x:c r="N11" s="37"/>
-      <x:c r="O11" s="37"/>
-      <x:c r="P11" s="37"/>
+      <x:c r="B11" s="19">
+        <x:v>46006</x:v>
+      </x:c>
+      <x:c r="C11" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D11" s="14">
+        <x:v>176870</x:v>
+      </x:c>
+      <x:c r="E11" s="18"/>
+      <x:c r="F11" s="18"/>
+      <x:c r="G11" s="18"/>
+      <x:c r="H11" s="18"/>
+      <x:c r="I11" s="18"/>
+      <x:c r="J11" s="18"/>
+      <x:c r="K11" s="18"/>
+      <x:c r="L11" s="18"/>
+      <x:c r="M11" s="18"/>
+      <x:c r="N11" s="18"/>
+      <x:c r="O11" s="18"/>
+      <x:c r="P11" s="18"/>
     </x:row>
     <x:row r="12" spans="2:16" ht="25.5" customHeight="1">
-      <x:c r="B12" s="9"/>
-      <x:c r="C12" s="10"/>
-      <x:c r="D12" s="14"/>
-      <x:c r="E12" s="37"/>
-      <x:c r="F12" s="37"/>
-      <x:c r="G12" s="37"/>
-      <x:c r="H12" s="37"/>
-      <x:c r="I12" s="37"/>
-      <x:c r="J12" s="37"/>
-      <x:c r="K12" s="37"/>
-      <x:c r="L12" s="37"/>
-      <x:c r="M12" s="37"/>
-      <x:c r="N12" s="37"/>
-      <x:c r="O12" s="37"/>
-      <x:c r="P12" s="37"/>
+      <x:c r="B12" s="19">
+        <x:v>46006</x:v>
+      </x:c>
+      <x:c r="C12" s="10" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D12" s="14">
+        <x:v>14720</x:v>
+      </x:c>
+      <x:c r="E12" s="18"/>
+      <x:c r="F12" s="18"/>
+      <x:c r="G12" s="18"/>
+      <x:c r="H12" s="18"/>
+      <x:c r="I12" s="18"/>
+      <x:c r="J12" s="18"/>
+      <x:c r="K12" s="18"/>
+      <x:c r="L12" s="18"/>
+      <x:c r="M12" s="18"/>
+      <x:c r="N12" s="18"/>
+      <x:c r="O12" s="18"/>
+      <x:c r="P12" s="18"/>
     </x:row>
     <x:row r="13" spans="2:16" ht="25.5" customHeight="1">
-      <x:c r="B13" s="9"/>
-      <x:c r="C13" s="10"/>
-      <x:c r="D13" s="14"/>
-      <x:c r="E13" s="37"/>
-      <x:c r="F13" s="37"/>
-      <x:c r="G13" s="37"/>
-      <x:c r="H13" s="37"/>
-      <x:c r="I13" s="37"/>
-      <x:c r="J13" s="37"/>
-      <x:c r="K13" s="37"/>
-      <x:c r="L13" s="37"/>
-      <x:c r="M13" s="37"/>
-      <x:c r="N13" s="37"/>
-      <x:c r="O13" s="37"/>
-      <x:c r="P13" s="37"/>
+      <x:c r="B13" s="19">
+        <x:v>46006</x:v>
+      </x:c>
+      <x:c r="C13" s="10" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D13" s="14">
+        <x:v>221090</x:v>
+      </x:c>
+      <x:c r="E13" s="18"/>
+      <x:c r="F13" s="18"/>
+      <x:c r="G13" s="18"/>
+      <x:c r="H13" s="18"/>
+      <x:c r="I13" s="18"/>
+      <x:c r="J13" s="18"/>
+      <x:c r="K13" s="18"/>
+      <x:c r="L13" s="18"/>
+      <x:c r="M13" s="18"/>
+      <x:c r="N13" s="18"/>
+      <x:c r="O13" s="18"/>
+      <x:c r="P13" s="18"/>
     </x:row>
     <x:row r="14" spans="2:16" ht="25.5" customHeight="1">
-      <x:c r="B14" s="9"/>
-      <x:c r="C14" s="10"/>
-      <x:c r="D14" s="14"/>
-      <x:c r="E14" s="37"/>
-      <x:c r="F14" s="37"/>
-      <x:c r="G14" s="37"/>
-      <x:c r="H14" s="37"/>
-      <x:c r="I14" s="37"/>
-      <x:c r="J14" s="37"/>
-      <x:c r="K14" s="37"/>
-      <x:c r="L14" s="37"/>
-      <x:c r="M14" s="37"/>
-      <x:c r="N14" s="37"/>
-      <x:c r="O14" s="37"/>
-      <x:c r="P14" s="37"/>
+      <x:c r="B14" s="19">
+        <x:v>46006</x:v>
+      </x:c>
+      <x:c r="C14" s="10" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D14" s="14">
+        <x:v>38310</x:v>
+      </x:c>
+      <x:c r="E14" s="18"/>
+      <x:c r="F14" s="18"/>
+      <x:c r="G14" s="18"/>
+      <x:c r="H14" s="18"/>
+      <x:c r="I14" s="18"/>
+      <x:c r="J14" s="18"/>
+      <x:c r="K14" s="18"/>
+      <x:c r="L14" s="18"/>
+      <x:c r="M14" s="18"/>
+      <x:c r="N14" s="18"/>
+      <x:c r="O14" s="18"/>
+      <x:c r="P14" s="18"/>
     </x:row>
     <x:row r="15" spans="2:16" ht="25.5" customHeight="1">
-      <x:c r="B15" s="9"/>
-      <x:c r="C15" s="10"/>
-      <x:c r="D15" s="14"/>
-      <x:c r="E15" s="37"/>
-      <x:c r="F15" s="37"/>
-      <x:c r="G15" s="37"/>
-      <x:c r="H15" s="37"/>
-      <x:c r="I15" s="37"/>
-      <x:c r="J15" s="37"/>
-      <x:c r="K15" s="37"/>
-      <x:c r="L15" s="37"/>
-      <x:c r="M15" s="37"/>
-      <x:c r="N15" s="37"/>
-      <x:c r="O15" s="37"/>
-      <x:c r="P15" s="37"/>
+      <x:c r="B15" s="19">
+        <x:v>46006</x:v>
+      </x:c>
+      <x:c r="C15" s="10" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D15" s="14">
+        <x:v>51570</x:v>
+      </x:c>
+      <x:c r="E15" s="18"/>
+      <x:c r="F15" s="18"/>
+      <x:c r="G15" s="18"/>
+      <x:c r="H15" s="18"/>
+      <x:c r="I15" s="18"/>
+      <x:c r="J15" s="18"/>
+      <x:c r="K15" s="18"/>
+      <x:c r="L15" s="18"/>
+      <x:c r="M15" s="18"/>
+      <x:c r="N15" s="18"/>
+      <x:c r="O15" s="18"/>
+      <x:c r="P15" s="18"/>
     </x:row>
     <x:row r="16" spans="2:16" ht="25.5" customHeight="1">
-      <x:c r="B16" s="9"/>
-      <x:c r="C16" s="10"/>
-      <x:c r="D16" s="14"/>
-      <x:c r="E16" s="37"/>
-      <x:c r="F16" s="37"/>
-      <x:c r="G16" s="37"/>
-      <x:c r="H16" s="37"/>
-      <x:c r="I16" s="37"/>
-      <x:c r="J16" s="37"/>
-      <x:c r="K16" s="37"/>
-      <x:c r="L16" s="37"/>
-      <x:c r="M16" s="37"/>
-      <x:c r="N16" s="37"/>
-      <x:c r="O16" s="37"/>
-      <x:c r="P16" s="37"/>
+      <x:c r="B16" s="19">
+        <x:v>46006</x:v>
+      </x:c>
+      <x:c r="C16" s="10" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="D16" s="14">
+        <x:v>14730</x:v>
+      </x:c>
+      <x:c r="E16" s="18"/>
+      <x:c r="F16" s="18"/>
+      <x:c r="G16" s="18"/>
+      <x:c r="H16" s="18"/>
+      <x:c r="I16" s="18"/>
+      <x:c r="J16" s="18"/>
+      <x:c r="K16" s="18"/>
+      <x:c r="L16" s="18"/>
+      <x:c r="M16" s="18"/>
+      <x:c r="N16" s="18"/>
+      <x:c r="O16" s="18"/>
+      <x:c r="P16" s="18"/>
     </x:row>
     <x:row r="17" spans="2:16" ht="25.5" customHeight="1">
       <x:c r="B17" s="9"/>
       <x:c r="C17" s="10"/>
       <x:c r="D17" s="14"/>
-      <x:c r="E17" s="37"/>
-      <x:c r="F17" s="37"/>
-      <x:c r="G17" s="37"/>
-      <x:c r="H17" s="37"/>
-      <x:c r="I17" s="37"/>
-      <x:c r="J17" s="37"/>
-      <x:c r="K17" s="37"/>
-      <x:c r="L17" s="37"/>
-      <x:c r="M17" s="37"/>
-      <x:c r="N17" s="37"/>
-      <x:c r="O17" s="37"/>
-      <x:c r="P17" s="37"/>
+      <x:c r="E17" s="18"/>
+      <x:c r="F17" s="18"/>
+      <x:c r="G17" s="18"/>
+      <x:c r="H17" s="18"/>
+      <x:c r="I17" s="18"/>
+      <x:c r="J17" s="18"/>
+      <x:c r="K17" s="18"/>
+      <x:c r="L17" s="18"/>
+      <x:c r="M17" s="18"/>
+      <x:c r="N17" s="18"/>
+      <x:c r="O17" s="18"/>
+      <x:c r="P17" s="18"/>
     </x:row>
     <x:row r="18" spans="2:16" ht="25.5" customHeight="1">
       <x:c r="B18" s="9"/>
       <x:c r="C18" s="10"/>
       <x:c r="D18" s="14"/>
-      <x:c r="E18" s="37"/>
-      <x:c r="F18" s="37"/>
-      <x:c r="G18" s="37"/>
-      <x:c r="H18" s="37"/>
-      <x:c r="I18" s="37"/>
-      <x:c r="J18" s="37"/>
-      <x:c r="K18" s="37"/>
-      <x:c r="L18" s="37"/>
-      <x:c r="M18" s="37"/>
-      <x:c r="N18" s="37"/>
-      <x:c r="O18" s="37"/>
-      <x:c r="P18" s="37"/>
+      <x:c r="E18" s="18"/>
+      <x:c r="F18" s="18"/>
+      <x:c r="G18" s="18"/>
+      <x:c r="H18" s="18"/>
+      <x:c r="I18" s="18"/>
+      <x:c r="J18" s="18"/>
+      <x:c r="K18" s="18"/>
+      <x:c r="L18" s="18"/>
+      <x:c r="M18" s="18"/>
+      <x:c r="N18" s="18"/>
+      <x:c r="O18" s="18"/>
+      <x:c r="P18" s="18"/>
     </x:row>
     <x:row r="19" spans="2:16" ht="25.5" customHeight="1">
       <x:c r="B19" s="9"/>
       <x:c r="C19" s="10"/>
       <x:c r="D19" s="14"/>
-      <x:c r="E19" s="37"/>
-      <x:c r="F19" s="37"/>
-      <x:c r="G19" s="37"/>
-      <x:c r="H19" s="37"/>
-      <x:c r="I19" s="37"/>
-      <x:c r="J19" s="37"/>
-      <x:c r="K19" s="37"/>
-      <x:c r="L19" s="37"/>
-      <x:c r="M19" s="37"/>
-      <x:c r="N19" s="37"/>
-      <x:c r="O19" s="37"/>
-      <x:c r="P19" s="37"/>
+      <x:c r="E19" s="18"/>
+      <x:c r="F19" s="18"/>
+      <x:c r="G19" s="18"/>
+      <x:c r="H19" s="18"/>
+      <x:c r="I19" s="18"/>
+      <x:c r="J19" s="18"/>
+      <x:c r="K19" s="18"/>
+      <x:c r="L19" s="18"/>
+      <x:c r="M19" s="18"/>
+      <x:c r="N19" s="18"/>
+      <x:c r="O19" s="18"/>
+      <x:c r="P19" s="18"/>
     </x:row>
     <x:row r="20" spans="2:16" ht="25.5" customHeight="1">
       <x:c r="B20" s="9"/>
       <x:c r="C20" s="10"/>
       <x:c r="D20" s="14"/>
-      <x:c r="E20" s="37"/>
-      <x:c r="F20" s="37"/>
-      <x:c r="G20" s="37"/>
-      <x:c r="H20" s="37"/>
-      <x:c r="I20" s="37"/>
-      <x:c r="J20" s="37"/>
-      <x:c r="K20" s="37"/>
-      <x:c r="L20" s="37"/>
-      <x:c r="M20" s="37"/>
-      <x:c r="N20" s="37"/>
-      <x:c r="O20" s="37"/>
-      <x:c r="P20" s="37"/>
+      <x:c r="E20" s="18"/>
+      <x:c r="F20" s="18"/>
+      <x:c r="G20" s="18"/>
+      <x:c r="H20" s="18"/>
+      <x:c r="I20" s="18"/>
+      <x:c r="J20" s="18"/>
+      <x:c r="K20" s="18"/>
+      <x:c r="L20" s="18"/>
+      <x:c r="M20" s="18"/>
+      <x:c r="N20" s="18"/>
+      <x:c r="O20" s="18"/>
+      <x:c r="P20" s="18"/>
     </x:row>
     <x:row r="21" spans="2:16" ht="25.5" customHeight="1">
       <x:c r="B21" s="9"/>
       <x:c r="C21" s="10"/>
       <x:c r="D21" s="14"/>
-      <x:c r="E21" s="37"/>
-      <x:c r="F21" s="37"/>
-      <x:c r="G21" s="37"/>
-      <x:c r="H21" s="37"/>
-      <x:c r="I21" s="37"/>
-      <x:c r="J21" s="37"/>
-      <x:c r="K21" s="37"/>
-      <x:c r="L21" s="37"/>
-      <x:c r="M21" s="37"/>
-      <x:c r="N21" s="37"/>
-      <x:c r="O21" s="37"/>
-      <x:c r="P21" s="37"/>
+      <x:c r="E21" s="18"/>
+      <x:c r="F21" s="18"/>
+      <x:c r="G21" s="18"/>
+      <x:c r="H21" s="18"/>
+      <x:c r="I21" s="18"/>
+      <x:c r="J21" s="18"/>
+      <x:c r="K21" s="18"/>
+      <x:c r="L21" s="18"/>
+      <x:c r="M21" s="18"/>
+      <x:c r="N21" s="18"/>
+      <x:c r="O21" s="18"/>
+      <x:c r="P21" s="18"/>
     </x:row>
     <x:row r="22" spans="2:16" ht="25.5" customHeight="1">
       <x:c r="B22" s="9"/>
       <x:c r="C22" s="10"/>
       <x:c r="D22" s="14"/>
-      <x:c r="E22" s="37"/>
-      <x:c r="F22" s="37"/>
-      <x:c r="G22" s="37"/>
-      <x:c r="H22" s="37"/>
-      <x:c r="I22" s="37"/>
-      <x:c r="J22" s="37"/>
-      <x:c r="K22" s="37"/>
-      <x:c r="L22" s="37"/>
-      <x:c r="M22" s="37"/>
-      <x:c r="N22" s="37"/>
-      <x:c r="O22" s="37"/>
-      <x:c r="P22" s="37"/>
+      <x:c r="E22" s="18"/>
+      <x:c r="F22" s="18"/>
+      <x:c r="G22" s="18"/>
+      <x:c r="H22" s="18"/>
+      <x:c r="I22" s="18"/>
+      <x:c r="J22" s="18"/>
+      <x:c r="K22" s="18"/>
+      <x:c r="L22" s="18"/>
+      <x:c r="M22" s="18"/>
+      <x:c r="N22" s="18"/>
+      <x:c r="O22" s="18"/>
+      <x:c r="P22" s="18"/>
     </x:row>
     <x:row r="23" spans="2:16" ht="25.5" customHeight="1">
       <x:c r="B23" s="9"/>
       <x:c r="C23" s="10"/>
       <x:c r="D23" s="14"/>
-      <x:c r="E23" s="37"/>
-      <x:c r="F23" s="37"/>
-      <x:c r="G23" s="37"/>
-      <x:c r="H23" s="37"/>
-      <x:c r="I23" s="37"/>
-      <x:c r="J23" s="37"/>
-      <x:c r="K23" s="37"/>
-      <x:c r="L23" s="37"/>
-      <x:c r="M23" s="37"/>
-      <x:c r="N23" s="37"/>
-      <x:c r="O23" s="37"/>
-      <x:c r="P23" s="37"/>
+      <x:c r="E23" s="18"/>
+      <x:c r="F23" s="18"/>
+      <x:c r="G23" s="18"/>
+      <x:c r="H23" s="18"/>
+      <x:c r="I23" s="18"/>
+      <x:c r="J23" s="18"/>
+      <x:c r="K23" s="18"/>
+      <x:c r="L23" s="18"/>
+      <x:c r="M23" s="18"/>
+      <x:c r="N23" s="18"/>
+      <x:c r="O23" s="18"/>
+      <x:c r="P23" s="18"/>
     </x:row>
     <x:row r="24" spans="2:16" ht="25.5" customHeight="1">
       <x:c r="B24" s="9"/>
@@ -1580,81 +1590,60 @@
     </x:row>
     <x:row r="27" spans="1:20" ht="25.5" customHeight="1">
       <x:c r="A27" s="15"/>
-      <x:c r="B27" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C27" s="34">
-        <x:f>SUM(D9:D26)</x:f>
-        <x:v>423020</x:v>
-      </x:c>
-      <x:c r="D27" s="20"/>
-      <x:c r="E27" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="F27" s="34">
-        <x:f>SUM(G9:G26)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G27" s="20"/>
-      <x:c r="H27" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="I27" s="34">
-        <x:f>SUM(J9:J26)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J27" s="20"/>
-      <x:c r="K27" s="18" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="L27" s="35">
-        <x:f>SUM(M9:M26)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M27" s="31"/>
-      <x:c r="N27" s="18" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="O27" s="35">
-        <x:f>SUM(P9:P26)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P27" s="31"/>
+      <x:c r="B27" s="18"/>
+      <x:c r="C27" s="18"/>
+      <x:c r="D27" s="18"/>
+      <x:c r="E27" s="18"/>
+      <x:c r="F27" s="18"/>
+      <x:c r="G27" s="18"/>
+      <x:c r="H27" s="18"/>
+      <x:c r="I27" s="18"/>
+      <x:c r="J27" s="18"/>
+      <x:c r="K27" s="18"/>
+      <x:c r="L27" s="18"/>
+      <x:c r="M27" s="18"/>
+      <x:c r="N27" s="18"/>
+      <x:c r="O27" s="18"/>
+      <x:c r="P27" s="18"/>
       <x:c r="Q27" s="15"/>
       <x:c r="R27" s="15"/>
       <x:c r="S27" s="15"/>
       <x:c r="T27" s="15"/>
     </x:row>
-    <x:row r="28" spans="4:4" ht="25.5" customHeight="1">
-      <x:c r="D28" s="1"/>
+    <x:row r="28" spans="2:16" ht="25.5" customHeight="1">
+      <x:c r="B28" s="18"/>
+      <x:c r="C28" s="18"/>
+      <x:c r="D28" s="18"/>
+      <x:c r="E28" s="18"/>
+      <x:c r="F28" s="18"/>
+      <x:c r="G28" s="18"/>
+      <x:c r="H28" s="18"/>
+      <x:c r="I28" s="18"/>
+      <x:c r="J28" s="18"/>
+      <x:c r="K28" s="18"/>
+      <x:c r="L28" s="18"/>
+      <x:c r="M28" s="18"/>
+      <x:c r="N28" s="18"/>
+      <x:c r="O28" s="18"/>
+      <x:c r="P28" s="18"/>
     </x:row>
     <x:row r="29" spans="1:23" ht="25.5" customHeight="1">
       <x:c r="A29" s="17"/>
-      <x:c r="B29" s="6" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C29" s="36">
-        <x:f>SUM(C27:D27,F27:G27,I27:J27)</x:f>
-        <x:v>423020</x:v>
-      </x:c>
-      <x:c r="D29" s="20"/>
-      <x:c r="E29" s="17"/>
-      <x:c r="F29" s="17"/>
-      <x:c r="G29" s="17"/>
-      <x:c r="H29" s="17"/>
-      <x:c r="I29" s="17"/>
-      <x:c r="J29" s="17"/>
-      <x:c r="K29" s="6" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="L29" s="35">
-        <x:f>SUM(L27:M27,O27:P27,C6,F6,I6)</x:f>
-        <x:v>576980</x:v>
-      </x:c>
-      <x:c r="M29" s="31"/>
-      <x:c r="N29" s="17"/>
-      <x:c r="O29" s="17"/>
-      <x:c r="P29" s="17"/>
+      <x:c r="B29" s="18"/>
+      <x:c r="C29" s="18"/>
+      <x:c r="D29" s="18"/>
+      <x:c r="E29" s="18"/>
+      <x:c r="F29" s="18"/>
+      <x:c r="G29" s="18"/>
+      <x:c r="H29" s="18"/>
+      <x:c r="I29" s="18"/>
+      <x:c r="J29" s="18"/>
+      <x:c r="K29" s="18"/>
+      <x:c r="L29" s="18"/>
+      <x:c r="M29" s="18"/>
+      <x:c r="N29" s="18"/>
+      <x:c r="O29" s="18"/>
+      <x:c r="P29" s="18"/>
       <x:c r="Q29" s="17"/>
       <x:c r="R29" s="17"/>
       <x:c r="S29" s="17"/>
@@ -4583,22 +4572,15 @@
       <x:c r="D1002" s="1"/>
     </x:row>
   </x:sheetData>
-  <x:mergeCells count="13">
+  <x:mergeCells count="6">
     <x:mergeCell ref="C1:D1"/>
     <x:mergeCell ref="B2:B3"/>
     <x:mergeCell ref="C2:D3"/>
     <x:mergeCell ref="C5:D5"/>
     <x:mergeCell ref="C6:D6"/>
     <x:mergeCell ref="B7:D7"/>
-    <x:mergeCell ref="C27:D27"/>
-    <x:mergeCell ref="F27:G27"/>
-    <x:mergeCell ref="I27:J27"/>
-    <x:mergeCell ref="L27:M27"/>
-    <x:mergeCell ref="O27:P27"/>
-    <x:mergeCell ref="C29:D29"/>
-    <x:mergeCell ref="L29:M29"/>
   </x:mergeCells>
-  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51152777671813964844" footer="0.51152777671813964844"/>
+  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51138889789581298828" footer="0.51138889789581298828"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="0" verticalDpi="0" copies="1"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="1" alignWithMargins="1"/>
 </x:worksheet>
@@ -4626,30 +4608,30 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="2:7" ht="25.5" customHeight="1">
-      <x:c r="B1" s="19"/>
-      <x:c r="C1" s="20"/>
+      <x:c r="B1" s="34"/>
+      <x:c r="C1" s="21"/>
       <x:c r="D1" s="1"/>
       <x:c r="E1" s="2" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F1" s="21"/>
-      <x:c r="G1" s="20"/>
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F1" s="20"/>
+      <x:c r="G1" s="21"/>
     </x:row>
     <x:row r="2" spans="2:9" ht="25.5" customHeight="1">
       <x:c r="B2" s="22" t="s">
-        <x:v>7</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C2" s="24">
         <x:f>SUM(F1:G1,-C29:D29)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D2" s="25"/>
-      <x:c r="F2" s="28" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="29"/>
-      <x:c r="H2" s="29"/>
-      <x:c r="I2" s="20"/>
+      <x:c r="F2" s="35" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G2" s="31"/>
+      <x:c r="H2" s="31"/>
+      <x:c r="I2" s="21"/>
     </x:row>
     <x:row r="3" spans="2:4" ht="10.5" customHeight="1">
       <x:c r="B3" s="23"/>
@@ -4661,118 +4643,118 @@
     </x:row>
     <x:row r="5" spans="2:13" ht="25.5" customHeight="1">
       <x:c r="B5" s="2" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C5" s="30"/>
-      <x:c r="D5" s="20"/>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C5" s="28"/>
+      <x:c r="D5" s="21"/>
       <x:c r="E5" s="3" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F5" s="30"/>
-      <x:c r="G5" s="20"/>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="F5" s="28"/>
+      <x:c r="G5" s="21"/>
       <x:c r="H5" s="3" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="I5" s="30"/>
-      <x:c r="J5" s="20"/>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="I5" s="28"/>
+      <x:c r="J5" s="21"/>
       <x:c r="K5" s="3" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="L5" s="30"/>
-      <x:c r="M5" s="20"/>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="L5" s="28"/>
+      <x:c r="M5" s="21"/>
     </x:row>
     <x:row r="6" spans="2:13" ht="25.5" customHeight="1">
       <x:c r="B6" s="4" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C6" s="32">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C6" s="29">
         <x:f>SUM(C5:D5,-C27:D27)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D6" s="20"/>
+      <x:c r="D6" s="21"/>
       <x:c r="E6" s="5" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="F6" s="32">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F6" s="29">
         <x:f>SUM(F5:G5,-F27:G27)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G6" s="20"/>
+      <x:c r="G6" s="21"/>
       <x:c r="H6" s="5" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="I6" s="32">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="I6" s="29">
         <x:f>SUM(I5:J5,-I27:J27)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J6" s="20"/>
+      <x:c r="J6" s="21"/>
       <x:c r="K6" s="5" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="L6" s="32">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="L6" s="29">
         <x:f>SUM(L5:M5,-L27:M27)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M6" s="20"/>
+      <x:c r="M6" s="21"/>
     </x:row>
     <x:row r="7" spans="2:13" ht="25.5" customHeight="1">
-      <x:c r="B7" s="33" t="s">
+      <x:c r="B7" s="30" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C7" s="31"/>
+      <x:c r="D7" s="21"/>
+      <x:c r="E7" s="30" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F7" s="31"/>
+      <x:c r="G7" s="21"/>
+      <x:c r="H7" s="30" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="I7" s="31"/>
+      <x:c r="J7" s="21"/>
+      <x:c r="K7" s="30" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C7" s="29"/>
-      <x:c r="D7" s="20"/>
-      <x:c r="E7" s="33" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="F7" s="29"/>
-      <x:c r="G7" s="20"/>
-      <x:c r="H7" s="33" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="I7" s="29"/>
-      <x:c r="J7" s="20"/>
-      <x:c r="K7" s="33" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="L7" s="29"/>
-      <x:c r="M7" s="20"/>
+      <x:c r="L7" s="31"/>
+      <x:c r="M7" s="21"/>
     </x:row>
     <x:row r="8" spans="2:13" ht="25.5" customHeight="1">
       <x:c r="B8" s="6" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C8" s="7" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D8" s="8" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C8" s="7" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D8" s="8" t="s">
-        <x:v>13</x:v>
-      </x:c>
       <x:c r="E8" s="6" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="F8" s="7" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G8" s="8" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="F8" s="7" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G8" s="8" t="s">
-        <x:v>13</x:v>
-      </x:c>
       <x:c r="H8" s="6" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I8" s="7" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="J8" s="8" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="I8" s="7" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="J8" s="8" t="s">
-        <x:v>13</x:v>
-      </x:c>
       <x:c r="K8" s="6" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="L8" s="7" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="M8" s="8" t="s">
         <x:v>10</x:v>
-      </x:c>
-      <x:c r="L8" s="7" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="M8" s="8" t="s">
-        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="2:13" ht="25.5" customHeight="1">
@@ -5030,37 +5012,37 @@
     <x:row r="27" spans="1:20" ht="25.5" customHeight="1">
       <x:c r="A27" s="15"/>
       <x:c r="B27" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C27" s="34">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C27" s="32">
         <x:f>SUM(D9:D26)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D27" s="20"/>
+      <x:c r="D27" s="21"/>
       <x:c r="E27" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="F27" s="34">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="F27" s="32">
         <x:f>SUM(G9:G26)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G27" s="20"/>
+      <x:c r="G27" s="21"/>
       <x:c r="H27" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="I27" s="34">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="I27" s="32">
         <x:f>SUM(J9:J26)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J27" s="20"/>
+      <x:c r="J27" s="21"/>
       <x:c r="K27" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="L27" s="34">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="L27" s="32">
         <x:f>SUM(M9:M26)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M27" s="20"/>
+      <x:c r="M27" s="21"/>
       <x:c r="N27" s="15"/>
       <x:c r="O27" s="15"/>
       <x:c r="P27" s="15"/>
@@ -5075,13 +5057,13 @@
     <x:row r="29" spans="1:23" ht="25.5" customHeight="1">
       <x:c r="A29" s="17"/>
       <x:c r="B29" s="6" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C29" s="36">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C29" s="33">
         <x:f>SUM(C27:D27,F27:G27,I27:J27,L27:M27)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D29" s="20"/>
+      <x:c r="D29" s="21"/>
       <x:c r="E29" s="17"/>
       <x:c r="F29" s="17"/>
       <x:c r="G29" s="17"/>
@@ -8046,7 +8028,7 @@
     <x:mergeCell ref="L27:M27"/>
     <x:mergeCell ref="C29:D29"/>
   </x:mergeCells>
-  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51152777671813964844" footer="0.51152777671813964844"/>
+  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51138889789581298828" footer="0.51138889789581298828"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="0" verticalDpi="0" copies="1"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="1" alignWithMargins="1"/>
 </x:worksheet>
@@ -8074,30 +8056,30 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="2:7" ht="25.5" customHeight="1">
-      <x:c r="B1" s="19"/>
-      <x:c r="C1" s="20"/>
+      <x:c r="B1" s="34"/>
+      <x:c r="C1" s="21"/>
       <x:c r="D1" s="1"/>
       <x:c r="E1" s="2" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F1" s="21"/>
-      <x:c r="G1" s="20"/>
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F1" s="20"/>
+      <x:c r="G1" s="21"/>
     </x:row>
     <x:row r="2" spans="2:9" ht="25.5" customHeight="1">
       <x:c r="B2" s="22" t="s">
-        <x:v>7</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C2" s="24">
         <x:f>SUM(F1:G1,-C29:D29)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D2" s="25"/>
-      <x:c r="F2" s="28" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="29"/>
-      <x:c r="H2" s="29"/>
-      <x:c r="I2" s="20"/>
+      <x:c r="F2" s="35" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G2" s="31"/>
+      <x:c r="H2" s="31"/>
+      <x:c r="I2" s="21"/>
     </x:row>
     <x:row r="3" spans="2:4" ht="10.5" customHeight="1">
       <x:c r="B3" s="23"/>
@@ -8109,118 +8091,118 @@
     </x:row>
     <x:row r="5" spans="2:13" ht="25.5" customHeight="1">
       <x:c r="B5" s="2" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C5" s="30"/>
-      <x:c r="D5" s="20"/>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C5" s="28"/>
+      <x:c r="D5" s="21"/>
       <x:c r="E5" s="3" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F5" s="30"/>
-      <x:c r="G5" s="20"/>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="F5" s="28"/>
+      <x:c r="G5" s="21"/>
       <x:c r="H5" s="3" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="I5" s="30"/>
-      <x:c r="J5" s="20"/>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="I5" s="28"/>
+      <x:c r="J5" s="21"/>
       <x:c r="K5" s="3" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="L5" s="30"/>
-      <x:c r="M5" s="20"/>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="L5" s="28"/>
+      <x:c r="M5" s="21"/>
     </x:row>
     <x:row r="6" spans="2:13" ht="25.5" customHeight="1">
       <x:c r="B6" s="4" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C6" s="32">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C6" s="29">
         <x:f>SUM(C5:D5,-C27:D27)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D6" s="20"/>
+      <x:c r="D6" s="21"/>
       <x:c r="E6" s="5" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="F6" s="32">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F6" s="29">
         <x:f>SUM(F5:G5,-F27:G27)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G6" s="20"/>
+      <x:c r="G6" s="21"/>
       <x:c r="H6" s="5" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="I6" s="32">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="I6" s="29">
         <x:f>SUM(I5:J5,-I27:J27)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J6" s="20"/>
+      <x:c r="J6" s="21"/>
       <x:c r="K6" s="5" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="L6" s="32">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="L6" s="29">
         <x:f>SUM(L5:M5,-L27:M27)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M6" s="20"/>
+      <x:c r="M6" s="21"/>
     </x:row>
     <x:row r="7" spans="2:13" ht="25.5" customHeight="1">
-      <x:c r="B7" s="33" t="s">
+      <x:c r="B7" s="30" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C7" s="31"/>
+      <x:c r="D7" s="21"/>
+      <x:c r="E7" s="30" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F7" s="31"/>
+      <x:c r="G7" s="21"/>
+      <x:c r="H7" s="30" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="I7" s="31"/>
+      <x:c r="J7" s="21"/>
+      <x:c r="K7" s="30" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C7" s="29"/>
-      <x:c r="D7" s="20"/>
-      <x:c r="E7" s="33" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="F7" s="29"/>
-      <x:c r="G7" s="20"/>
-      <x:c r="H7" s="33" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="I7" s="29"/>
-      <x:c r="J7" s="20"/>
-      <x:c r="K7" s="33" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="L7" s="29"/>
-      <x:c r="M7" s="20"/>
+      <x:c r="L7" s="31"/>
+      <x:c r="M7" s="21"/>
     </x:row>
     <x:row r="8" spans="2:13" ht="25.5" customHeight="1">
       <x:c r="B8" s="6" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C8" s="7" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D8" s="8" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C8" s="7" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D8" s="8" t="s">
-        <x:v>13</x:v>
-      </x:c>
       <x:c r="E8" s="6" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="F8" s="7" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G8" s="8" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="F8" s="7" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G8" s="8" t="s">
-        <x:v>13</x:v>
-      </x:c>
       <x:c r="H8" s="6" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I8" s="7" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="J8" s="8" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="I8" s="7" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="J8" s="8" t="s">
-        <x:v>13</x:v>
-      </x:c>
       <x:c r="K8" s="6" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="L8" s="7" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="M8" s="8" t="s">
         <x:v>10</x:v>
-      </x:c>
-      <x:c r="L8" s="7" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="M8" s="8" t="s">
-        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="2:13" ht="25.5" customHeight="1">
@@ -8478,37 +8460,37 @@
     <x:row r="27" spans="1:20" ht="25.5" customHeight="1">
       <x:c r="A27" s="15"/>
       <x:c r="B27" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C27" s="34">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C27" s="32">
         <x:f>SUM(D9:D26)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D27" s="20"/>
+      <x:c r="D27" s="21"/>
       <x:c r="E27" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="F27" s="34">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="F27" s="32">
         <x:f>SUM(G9:G26)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G27" s="20"/>
+      <x:c r="G27" s="21"/>
       <x:c r="H27" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="I27" s="34">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="I27" s="32">
         <x:f>SUM(J9:J26)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J27" s="20"/>
+      <x:c r="J27" s="21"/>
       <x:c r="K27" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="L27" s="34">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="L27" s="32">
         <x:f>SUM(M9:M26)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M27" s="20"/>
+      <x:c r="M27" s="21"/>
       <x:c r="N27" s="15"/>
       <x:c r="O27" s="15"/>
       <x:c r="P27" s="15"/>
@@ -8523,13 +8505,13 @@
     <x:row r="29" spans="1:23" ht="25.5" customHeight="1">
       <x:c r="A29" s="17"/>
       <x:c r="B29" s="6" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C29" s="36">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C29" s="33">
         <x:f>SUM(C27:D27,F27:G27,I27:J27,L27:M27)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D29" s="20"/>
+      <x:c r="D29" s="21"/>
       <x:c r="E29" s="17"/>
       <x:c r="F29" s="17"/>
       <x:c r="G29" s="17"/>
@@ -11494,7 +11476,7 @@
     <x:mergeCell ref="L27:M27"/>
     <x:mergeCell ref="C29:D29"/>
   </x:mergeCells>
-  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51152777671813964844" footer="0.51152777671813964844"/>
+  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51138889789581298828" footer="0.51138889789581298828"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="0" verticalDpi="0" copies="1"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="1" alignWithMargins="1"/>
 </x:worksheet>
@@ -11522,30 +11504,30 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="2:7" ht="25.5" customHeight="1">
-      <x:c r="B1" s="19"/>
-      <x:c r="C1" s="20"/>
+      <x:c r="B1" s="34"/>
+      <x:c r="C1" s="21"/>
       <x:c r="D1" s="1"/>
       <x:c r="E1" s="2" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F1" s="21"/>
-      <x:c r="G1" s="20"/>
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F1" s="20"/>
+      <x:c r="G1" s="21"/>
     </x:row>
     <x:row r="2" spans="2:9" ht="25.5" customHeight="1">
       <x:c r="B2" s="22" t="s">
-        <x:v>7</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C2" s="24">
         <x:f>SUM(F1:G1,-C29:D29)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D2" s="25"/>
-      <x:c r="F2" s="28" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="29"/>
-      <x:c r="H2" s="29"/>
-      <x:c r="I2" s="20"/>
+      <x:c r="F2" s="35" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G2" s="31"/>
+      <x:c r="H2" s="31"/>
+      <x:c r="I2" s="21"/>
     </x:row>
     <x:row r="3" spans="2:4" ht="10.5" customHeight="1">
       <x:c r="B3" s="23"/>
@@ -11557,118 +11539,118 @@
     </x:row>
     <x:row r="5" spans="2:13" ht="25.5" customHeight="1">
       <x:c r="B5" s="2" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C5" s="30"/>
-      <x:c r="D5" s="20"/>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C5" s="28"/>
+      <x:c r="D5" s="21"/>
       <x:c r="E5" s="3" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F5" s="30"/>
-      <x:c r="G5" s="20"/>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="F5" s="28"/>
+      <x:c r="G5" s="21"/>
       <x:c r="H5" s="3" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="I5" s="30"/>
-      <x:c r="J5" s="20"/>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="I5" s="28"/>
+      <x:c r="J5" s="21"/>
       <x:c r="K5" s="3" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="L5" s="30"/>
-      <x:c r="M5" s="20"/>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="L5" s="28"/>
+      <x:c r="M5" s="21"/>
     </x:row>
     <x:row r="6" spans="2:13" ht="25.5" customHeight="1">
       <x:c r="B6" s="4" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C6" s="32">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C6" s="29">
         <x:f>SUM(C5:D5,-C27:D27)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D6" s="20"/>
+      <x:c r="D6" s="21"/>
       <x:c r="E6" s="5" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="F6" s="32">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F6" s="29">
         <x:f>SUM(F5:G5,-F27:G27)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G6" s="20"/>
+      <x:c r="G6" s="21"/>
       <x:c r="H6" s="5" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="I6" s="32">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="I6" s="29">
         <x:f>SUM(I5:J5,-I27:J27)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J6" s="20"/>
+      <x:c r="J6" s="21"/>
       <x:c r="K6" s="5" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="L6" s="32">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="L6" s="29">
         <x:f>SUM(L5:M5,-L27:M27)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M6" s="20"/>
+      <x:c r="M6" s="21"/>
     </x:row>
     <x:row r="7" spans="2:13" ht="25.5" customHeight="1">
-      <x:c r="B7" s="33" t="s">
+      <x:c r="B7" s="30" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C7" s="31"/>
+      <x:c r="D7" s="21"/>
+      <x:c r="E7" s="30" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F7" s="31"/>
+      <x:c r="G7" s="21"/>
+      <x:c r="H7" s="30" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="I7" s="31"/>
+      <x:c r="J7" s="21"/>
+      <x:c r="K7" s="30" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C7" s="29"/>
-      <x:c r="D7" s="20"/>
-      <x:c r="E7" s="33" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="F7" s="29"/>
-      <x:c r="G7" s="20"/>
-      <x:c r="H7" s="33" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="I7" s="29"/>
-      <x:c r="J7" s="20"/>
-      <x:c r="K7" s="33" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="L7" s="29"/>
-      <x:c r="M7" s="20"/>
+      <x:c r="L7" s="31"/>
+      <x:c r="M7" s="21"/>
     </x:row>
     <x:row r="8" spans="2:13" ht="25.5" customHeight="1">
       <x:c r="B8" s="6" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C8" s="7" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D8" s="8" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C8" s="7" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D8" s="8" t="s">
-        <x:v>13</x:v>
-      </x:c>
       <x:c r="E8" s="6" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="F8" s="7" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G8" s="8" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="F8" s="7" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G8" s="8" t="s">
-        <x:v>13</x:v>
-      </x:c>
       <x:c r="H8" s="6" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I8" s="7" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="J8" s="8" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="I8" s="7" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="J8" s="8" t="s">
-        <x:v>13</x:v>
-      </x:c>
       <x:c r="K8" s="6" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="L8" s="7" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="M8" s="8" t="s">
         <x:v>10</x:v>
-      </x:c>
-      <x:c r="L8" s="7" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="M8" s="8" t="s">
-        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="2:13" ht="25.5" customHeight="1">
@@ -11926,37 +11908,37 @@
     <x:row r="27" spans="1:20" ht="25.5" customHeight="1">
       <x:c r="A27" s="15"/>
       <x:c r="B27" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C27" s="34">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C27" s="32">
         <x:f>SUM(D9:D26)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D27" s="20"/>
+      <x:c r="D27" s="21"/>
       <x:c r="E27" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="F27" s="34">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="F27" s="32">
         <x:f>SUM(G9:G26)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G27" s="20"/>
+      <x:c r="G27" s="21"/>
       <x:c r="H27" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="I27" s="34">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="I27" s="32">
         <x:f>SUM(J9:J26)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J27" s="20"/>
+      <x:c r="J27" s="21"/>
       <x:c r="K27" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="L27" s="34">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="L27" s="32">
         <x:f>SUM(M9:M26)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M27" s="20"/>
+      <x:c r="M27" s="21"/>
       <x:c r="N27" s="15"/>
       <x:c r="O27" s="15"/>
       <x:c r="P27" s="15"/>
@@ -11971,13 +11953,13 @@
     <x:row r="29" spans="1:23" ht="25.5" customHeight="1">
       <x:c r="A29" s="17"/>
       <x:c r="B29" s="6" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C29" s="36">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C29" s="33">
         <x:f>SUM(C27:D27,F27:G27,I27:J27,L27:M27)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D29" s="20"/>
+      <x:c r="D29" s="21"/>
       <x:c r="E29" s="17"/>
       <x:c r="F29" s="17"/>
       <x:c r="G29" s="17"/>
@@ -14942,7 +14924,7 @@
     <x:mergeCell ref="L27:M27"/>
     <x:mergeCell ref="C29:D29"/>
   </x:mergeCells>
-  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51152777671813964844" footer="0.51152777671813964844"/>
+  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51138889789581298828" footer="0.51138889789581298828"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="0" verticalDpi="0" copies="1"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="1" alignWithMargins="1"/>
 </x:worksheet>
@@ -14970,30 +14952,30 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="2:7" ht="25.5" customHeight="1">
-      <x:c r="B1" s="19"/>
-      <x:c r="C1" s="20"/>
+      <x:c r="B1" s="34"/>
+      <x:c r="C1" s="21"/>
       <x:c r="D1" s="1"/>
       <x:c r="E1" s="2" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F1" s="21"/>
-      <x:c r="G1" s="20"/>
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F1" s="20"/>
+      <x:c r="G1" s="21"/>
     </x:row>
     <x:row r="2" spans="2:9" ht="25.5" customHeight="1">
       <x:c r="B2" s="22" t="s">
-        <x:v>7</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C2" s="24">
         <x:f>SUM(F1:G1,-C29:D29)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D2" s="25"/>
-      <x:c r="F2" s="28" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="29"/>
-      <x:c r="H2" s="29"/>
-      <x:c r="I2" s="20"/>
+      <x:c r="F2" s="35" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G2" s="31"/>
+      <x:c r="H2" s="31"/>
+      <x:c r="I2" s="21"/>
     </x:row>
     <x:row r="3" spans="2:4" ht="10.5" customHeight="1">
       <x:c r="B3" s="23"/>
@@ -15005,118 +14987,118 @@
     </x:row>
     <x:row r="5" spans="2:13" ht="25.5" customHeight="1">
       <x:c r="B5" s="2" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C5" s="30"/>
-      <x:c r="D5" s="20"/>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C5" s="28"/>
+      <x:c r="D5" s="21"/>
       <x:c r="E5" s="3" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F5" s="30"/>
-      <x:c r="G5" s="20"/>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="F5" s="28"/>
+      <x:c r="G5" s="21"/>
       <x:c r="H5" s="3" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="I5" s="30"/>
-      <x:c r="J5" s="20"/>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="I5" s="28"/>
+      <x:c r="J5" s="21"/>
       <x:c r="K5" s="3" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="L5" s="30"/>
-      <x:c r="M5" s="20"/>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="L5" s="28"/>
+      <x:c r="M5" s="21"/>
     </x:row>
     <x:row r="6" spans="2:13" ht="25.5" customHeight="1">
       <x:c r="B6" s="4" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C6" s="32">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C6" s="29">
         <x:f>SUM(C5:D5,-C27:D27)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D6" s="20"/>
+      <x:c r="D6" s="21"/>
       <x:c r="E6" s="5" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="F6" s="32">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F6" s="29">
         <x:f>SUM(F5:G5,-F27:G27)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G6" s="20"/>
+      <x:c r="G6" s="21"/>
       <x:c r="H6" s="5" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="I6" s="32">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="I6" s="29">
         <x:f>SUM(I5:J5,-I27:J27)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J6" s="20"/>
+      <x:c r="J6" s="21"/>
       <x:c r="K6" s="5" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="L6" s="32">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="L6" s="29">
         <x:f>SUM(L5:M5,-L27:M27)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M6" s="20"/>
+      <x:c r="M6" s="21"/>
     </x:row>
     <x:row r="7" spans="2:13" ht="25.5" customHeight="1">
-      <x:c r="B7" s="33" t="s">
+      <x:c r="B7" s="30" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C7" s="31"/>
+      <x:c r="D7" s="21"/>
+      <x:c r="E7" s="30" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F7" s="31"/>
+      <x:c r="G7" s="21"/>
+      <x:c r="H7" s="30" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="I7" s="31"/>
+      <x:c r="J7" s="21"/>
+      <x:c r="K7" s="30" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C7" s="29"/>
-      <x:c r="D7" s="20"/>
-      <x:c r="E7" s="33" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="F7" s="29"/>
-      <x:c r="G7" s="20"/>
-      <x:c r="H7" s="33" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="I7" s="29"/>
-      <x:c r="J7" s="20"/>
-      <x:c r="K7" s="33" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="L7" s="29"/>
-      <x:c r="M7" s="20"/>
+      <x:c r="L7" s="31"/>
+      <x:c r="M7" s="21"/>
     </x:row>
     <x:row r="8" spans="2:13" ht="25.5" customHeight="1">
       <x:c r="B8" s="6" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C8" s="7" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D8" s="8" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C8" s="7" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D8" s="8" t="s">
-        <x:v>13</x:v>
-      </x:c>
       <x:c r="E8" s="6" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="F8" s="7" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G8" s="8" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="F8" s="7" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G8" s="8" t="s">
-        <x:v>13</x:v>
-      </x:c>
       <x:c r="H8" s="6" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I8" s="7" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="J8" s="8" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="I8" s="7" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="J8" s="8" t="s">
-        <x:v>13</x:v>
-      </x:c>
       <x:c r="K8" s="6" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="L8" s="7" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="M8" s="8" t="s">
         <x:v>10</x:v>
-      </x:c>
-      <x:c r="L8" s="7" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="M8" s="8" t="s">
-        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="2:13" ht="25.5" customHeight="1">
@@ -15374,37 +15356,37 @@
     <x:row r="27" spans="1:20" ht="25.5" customHeight="1">
       <x:c r="A27" s="15"/>
       <x:c r="B27" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C27" s="34">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C27" s="32">
         <x:f>SUM(D9:D26)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D27" s="20"/>
+      <x:c r="D27" s="21"/>
       <x:c r="E27" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="F27" s="34">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="F27" s="32">
         <x:f>SUM(G9:G26)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G27" s="20"/>
+      <x:c r="G27" s="21"/>
       <x:c r="H27" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="I27" s="34">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="I27" s="32">
         <x:f>SUM(J9:J26)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J27" s="20"/>
+      <x:c r="J27" s="21"/>
       <x:c r="K27" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="L27" s="34">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="L27" s="32">
         <x:f>SUM(M9:M26)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M27" s="20"/>
+      <x:c r="M27" s="21"/>
       <x:c r="N27" s="15"/>
       <x:c r="O27" s="15"/>
       <x:c r="P27" s="15"/>
@@ -15419,13 +15401,13 @@
     <x:row r="29" spans="1:23" ht="25.5" customHeight="1">
       <x:c r="A29" s="17"/>
       <x:c r="B29" s="6" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C29" s="36">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C29" s="33">
         <x:f>SUM(C27:D27,F27:G27,I27:J27,L27:M27)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D29" s="20"/>
+      <x:c r="D29" s="21"/>
       <x:c r="E29" s="17"/>
       <x:c r="F29" s="17"/>
       <x:c r="G29" s="17"/>
@@ -18390,7 +18372,7 @@
     <x:mergeCell ref="L27:M27"/>
     <x:mergeCell ref="C29:D29"/>
   </x:mergeCells>
-  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51152777671813964844" footer="0.51152777671813964844"/>
+  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51138889789581298828" footer="0.51138889789581298828"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="0" verticalDpi="0" copies="1"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="1" alignWithMargins="1"/>
 </x:worksheet>
@@ -18418,30 +18400,30 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="2:7" ht="25.5" customHeight="1">
-      <x:c r="B1" s="19"/>
-      <x:c r="C1" s="20"/>
+      <x:c r="B1" s="34"/>
+      <x:c r="C1" s="21"/>
       <x:c r="D1" s="1"/>
       <x:c r="E1" s="2" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F1" s="21"/>
-      <x:c r="G1" s="20"/>
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F1" s="20"/>
+      <x:c r="G1" s="21"/>
     </x:row>
     <x:row r="2" spans="2:9" ht="25.5" customHeight="1">
       <x:c r="B2" s="22" t="s">
-        <x:v>7</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C2" s="24">
         <x:f>SUM(F1:G1,-C29:D29)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D2" s="25"/>
-      <x:c r="F2" s="28" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="29"/>
-      <x:c r="H2" s="29"/>
-      <x:c r="I2" s="20"/>
+      <x:c r="F2" s="35" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G2" s="31"/>
+      <x:c r="H2" s="31"/>
+      <x:c r="I2" s="21"/>
     </x:row>
     <x:row r="3" spans="2:4" ht="10.5" customHeight="1">
       <x:c r="B3" s="23"/>
@@ -18453,118 +18435,118 @@
     </x:row>
     <x:row r="5" spans="2:13" ht="25.5" customHeight="1">
       <x:c r="B5" s="2" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C5" s="30"/>
-      <x:c r="D5" s="20"/>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C5" s="28"/>
+      <x:c r="D5" s="21"/>
       <x:c r="E5" s="3" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F5" s="30"/>
-      <x:c r="G5" s="20"/>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="F5" s="28"/>
+      <x:c r="G5" s="21"/>
       <x:c r="H5" s="3" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="I5" s="30"/>
-      <x:c r="J5" s="20"/>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="I5" s="28"/>
+      <x:c r="J5" s="21"/>
       <x:c r="K5" s="3" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="L5" s="30"/>
-      <x:c r="M5" s="20"/>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="L5" s="28"/>
+      <x:c r="M5" s="21"/>
     </x:row>
     <x:row r="6" spans="2:13" ht="25.5" customHeight="1">
       <x:c r="B6" s="4" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C6" s="32">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C6" s="29">
         <x:f>SUM(C5:D5,-C27:D27)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D6" s="20"/>
+      <x:c r="D6" s="21"/>
       <x:c r="E6" s="5" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="F6" s="32">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F6" s="29">
         <x:f>SUM(F5:G5,-F27:G27)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G6" s="20"/>
+      <x:c r="G6" s="21"/>
       <x:c r="H6" s="5" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="I6" s="32">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="I6" s="29">
         <x:f>SUM(I5:J5,-I27:J27)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J6" s="20"/>
+      <x:c r="J6" s="21"/>
       <x:c r="K6" s="5" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="L6" s="32">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="L6" s="29">
         <x:f>SUM(L5:M5,-L27:M27)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M6" s="20"/>
+      <x:c r="M6" s="21"/>
     </x:row>
     <x:row r="7" spans="2:13" ht="25.5" customHeight="1">
-      <x:c r="B7" s="33" t="s">
+      <x:c r="B7" s="30" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C7" s="31"/>
+      <x:c r="D7" s="21"/>
+      <x:c r="E7" s="30" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F7" s="31"/>
+      <x:c r="G7" s="21"/>
+      <x:c r="H7" s="30" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="I7" s="31"/>
+      <x:c r="J7" s="21"/>
+      <x:c r="K7" s="30" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C7" s="29"/>
-      <x:c r="D7" s="20"/>
-      <x:c r="E7" s="33" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="F7" s="29"/>
-      <x:c r="G7" s="20"/>
-      <x:c r="H7" s="33" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="I7" s="29"/>
-      <x:c r="J7" s="20"/>
-      <x:c r="K7" s="33" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="L7" s="29"/>
-      <x:c r="M7" s="20"/>
+      <x:c r="L7" s="31"/>
+      <x:c r="M7" s="21"/>
     </x:row>
     <x:row r="8" spans="2:13" ht="25.5" customHeight="1">
       <x:c r="B8" s="6" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C8" s="7" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D8" s="8" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C8" s="7" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D8" s="8" t="s">
-        <x:v>13</x:v>
-      </x:c>
       <x:c r="E8" s="6" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="F8" s="7" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G8" s="8" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="F8" s="7" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G8" s="8" t="s">
-        <x:v>13</x:v>
-      </x:c>
       <x:c r="H8" s="6" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I8" s="7" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="J8" s="8" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="I8" s="7" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="J8" s="8" t="s">
-        <x:v>13</x:v>
-      </x:c>
       <x:c r="K8" s="6" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="L8" s="7" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="M8" s="8" t="s">
         <x:v>10</x:v>
-      </x:c>
-      <x:c r="L8" s="7" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="M8" s="8" t="s">
-        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="2:13" ht="25.5" customHeight="1">
@@ -18822,37 +18804,37 @@
     <x:row r="27" spans="1:20" ht="25.5" customHeight="1">
       <x:c r="A27" s="15"/>
       <x:c r="B27" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C27" s="34">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C27" s="32">
         <x:f>SUM(D9:D26)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D27" s="20"/>
+      <x:c r="D27" s="21"/>
       <x:c r="E27" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="F27" s="34">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="F27" s="32">
         <x:f>SUM(G9:G26)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G27" s="20"/>
+      <x:c r="G27" s="21"/>
       <x:c r="H27" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="I27" s="34">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="I27" s="32">
         <x:f>SUM(J9:J26)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J27" s="20"/>
+      <x:c r="J27" s="21"/>
       <x:c r="K27" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="L27" s="34">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="L27" s="32">
         <x:f>SUM(M9:M26)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M27" s="20"/>
+      <x:c r="M27" s="21"/>
       <x:c r="N27" s="15"/>
       <x:c r="O27" s="15"/>
       <x:c r="P27" s="15"/>
@@ -18867,13 +18849,13 @@
     <x:row r="29" spans="1:23" ht="25.5" customHeight="1">
       <x:c r="A29" s="17"/>
       <x:c r="B29" s="6" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C29" s="36">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C29" s="33">
         <x:f>SUM(C27:D27,F27:G27,I27:J27,L27:M27)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D29" s="20"/>
+      <x:c r="D29" s="21"/>
       <x:c r="E29" s="17"/>
       <x:c r="F29" s="17"/>
       <x:c r="G29" s="17"/>
@@ -21838,7 +21820,7 @@
     <x:mergeCell ref="L27:M27"/>
     <x:mergeCell ref="C29:D29"/>
   </x:mergeCells>
-  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51152777671813964844" footer="0.51152777671813964844"/>
+  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51138889789581298828" footer="0.51138889789581298828"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="0" verticalDpi="0" copies="1"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="1" alignWithMargins="1"/>
 </x:worksheet>
@@ -21866,30 +21848,30 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="2:7" ht="25.5" customHeight="1">
-      <x:c r="B1" s="19"/>
-      <x:c r="C1" s="20"/>
+      <x:c r="B1" s="34"/>
+      <x:c r="C1" s="21"/>
       <x:c r="D1" s="1"/>
       <x:c r="E1" s="2" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F1" s="21"/>
-      <x:c r="G1" s="20"/>
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F1" s="20"/>
+      <x:c r="G1" s="21"/>
     </x:row>
     <x:row r="2" spans="2:9" ht="25.5" customHeight="1">
       <x:c r="B2" s="22" t="s">
-        <x:v>7</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C2" s="24">
         <x:f>SUM(F1:G1,-C29:D29)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D2" s="25"/>
-      <x:c r="F2" s="28" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="29"/>
-      <x:c r="H2" s="29"/>
-      <x:c r="I2" s="20"/>
+      <x:c r="F2" s="35" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G2" s="31"/>
+      <x:c r="H2" s="31"/>
+      <x:c r="I2" s="21"/>
     </x:row>
     <x:row r="3" spans="2:4" ht="10.5" customHeight="1">
       <x:c r="B3" s="23"/>
@@ -21901,118 +21883,118 @@
     </x:row>
     <x:row r="5" spans="2:13" ht="25.5" customHeight="1">
       <x:c r="B5" s="2" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C5" s="30"/>
-      <x:c r="D5" s="20"/>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C5" s="28"/>
+      <x:c r="D5" s="21"/>
       <x:c r="E5" s="3" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F5" s="30"/>
-      <x:c r="G5" s="20"/>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="F5" s="28"/>
+      <x:c r="G5" s="21"/>
       <x:c r="H5" s="3" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="I5" s="30"/>
-      <x:c r="J5" s="20"/>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="I5" s="28"/>
+      <x:c r="J5" s="21"/>
       <x:c r="K5" s="3" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="L5" s="30"/>
-      <x:c r="M5" s="20"/>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="L5" s="28"/>
+      <x:c r="M5" s="21"/>
     </x:row>
     <x:row r="6" spans="2:13" ht="25.5" customHeight="1">
       <x:c r="B6" s="4" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C6" s="32">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C6" s="29">
         <x:f>SUM(C5:D5,-C27:D27)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D6" s="20"/>
+      <x:c r="D6" s="21"/>
       <x:c r="E6" s="5" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="F6" s="32">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F6" s="29">
         <x:f>SUM(F5:G5,-F27:G27)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G6" s="20"/>
+      <x:c r="G6" s="21"/>
       <x:c r="H6" s="5" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="I6" s="32">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="I6" s="29">
         <x:f>SUM(I5:J5,-I27:J27)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J6" s="20"/>
+      <x:c r="J6" s="21"/>
       <x:c r="K6" s="5" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="L6" s="32">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="L6" s="29">
         <x:f>SUM(L5:M5,-L27:M27)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M6" s="20"/>
+      <x:c r="M6" s="21"/>
     </x:row>
     <x:row r="7" spans="2:13" ht="25.5" customHeight="1">
-      <x:c r="B7" s="33" t="s">
+      <x:c r="B7" s="30" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C7" s="31"/>
+      <x:c r="D7" s="21"/>
+      <x:c r="E7" s="30" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F7" s="31"/>
+      <x:c r="G7" s="21"/>
+      <x:c r="H7" s="30" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="I7" s="31"/>
+      <x:c r="J7" s="21"/>
+      <x:c r="K7" s="30" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C7" s="29"/>
-      <x:c r="D7" s="20"/>
-      <x:c r="E7" s="33" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="F7" s="29"/>
-      <x:c r="G7" s="20"/>
-      <x:c r="H7" s="33" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="I7" s="29"/>
-      <x:c r="J7" s="20"/>
-      <x:c r="K7" s="33" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="L7" s="29"/>
-      <x:c r="M7" s="20"/>
+      <x:c r="L7" s="31"/>
+      <x:c r="M7" s="21"/>
     </x:row>
     <x:row r="8" spans="2:13" ht="25.5" customHeight="1">
       <x:c r="B8" s="6" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C8" s="7" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D8" s="8" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C8" s="7" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D8" s="8" t="s">
-        <x:v>13</x:v>
-      </x:c>
       <x:c r="E8" s="6" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="F8" s="7" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G8" s="8" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="F8" s="7" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G8" s="8" t="s">
-        <x:v>13</x:v>
-      </x:c>
       <x:c r="H8" s="6" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I8" s="7" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="J8" s="8" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="I8" s="7" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="J8" s="8" t="s">
-        <x:v>13</x:v>
-      </x:c>
       <x:c r="K8" s="6" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="L8" s="7" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="M8" s="8" t="s">
         <x:v>10</x:v>
-      </x:c>
-      <x:c r="L8" s="7" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="M8" s="8" t="s">
-        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="2:13" ht="25.5" customHeight="1">
@@ -22270,37 +22252,37 @@
     <x:row r="27" spans="1:20" ht="25.5" customHeight="1">
       <x:c r="A27" s="15"/>
       <x:c r="B27" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C27" s="34">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C27" s="32">
         <x:f>SUM(D9:D26)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D27" s="20"/>
+      <x:c r="D27" s="21"/>
       <x:c r="E27" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="F27" s="34">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="F27" s="32">
         <x:f>SUM(G9:G26)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G27" s="20"/>
+      <x:c r="G27" s="21"/>
       <x:c r="H27" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="I27" s="34">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="I27" s="32">
         <x:f>SUM(J9:J26)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J27" s="20"/>
+      <x:c r="J27" s="21"/>
       <x:c r="K27" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="L27" s="34">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="L27" s="32">
         <x:f>SUM(M9:M26)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M27" s="20"/>
+      <x:c r="M27" s="21"/>
       <x:c r="N27" s="15"/>
       <x:c r="O27" s="15"/>
       <x:c r="P27" s="15"/>
@@ -22315,13 +22297,13 @@
     <x:row r="29" spans="1:23" ht="25.5" customHeight="1">
       <x:c r="A29" s="17"/>
       <x:c r="B29" s="6" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C29" s="36">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C29" s="33">
         <x:f>SUM(C27:D27,F27:G27,I27:J27,L27:M27)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D29" s="20"/>
+      <x:c r="D29" s="21"/>
       <x:c r="E29" s="17"/>
       <x:c r="F29" s="17"/>
       <x:c r="G29" s="17"/>
@@ -25286,7 +25268,7 @@
     <x:mergeCell ref="L27:M27"/>
     <x:mergeCell ref="C29:D29"/>
   </x:mergeCells>
-  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51152777671813964844" footer="0.51152777671813964844"/>
+  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51138889789581298828" footer="0.51138889789581298828"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="0" verticalDpi="0" copies="1"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="1" alignWithMargins="1"/>
 </x:worksheet>
@@ -25314,30 +25296,30 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="2:7" ht="25.5" customHeight="1">
-      <x:c r="B1" s="19"/>
-      <x:c r="C1" s="20"/>
+      <x:c r="B1" s="34"/>
+      <x:c r="C1" s="21"/>
       <x:c r="D1" s="1"/>
       <x:c r="E1" s="2" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F1" s="21"/>
-      <x:c r="G1" s="20"/>
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F1" s="20"/>
+      <x:c r="G1" s="21"/>
     </x:row>
     <x:row r="2" spans="2:9" ht="25.5" customHeight="1">
       <x:c r="B2" s="22" t="s">
-        <x:v>7</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C2" s="24">
         <x:f>SUM(F1:G1,-C29:D29)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D2" s="25"/>
-      <x:c r="F2" s="28" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="29"/>
-      <x:c r="H2" s="29"/>
-      <x:c r="I2" s="20"/>
+      <x:c r="F2" s="35" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G2" s="31"/>
+      <x:c r="H2" s="31"/>
+      <x:c r="I2" s="21"/>
     </x:row>
     <x:row r="3" spans="2:4" ht="10.5" customHeight="1">
       <x:c r="B3" s="23"/>
@@ -25349,118 +25331,118 @@
     </x:row>
     <x:row r="5" spans="2:13" ht="25.5" customHeight="1">
       <x:c r="B5" s="2" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C5" s="30"/>
-      <x:c r="D5" s="20"/>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C5" s="28"/>
+      <x:c r="D5" s="21"/>
       <x:c r="E5" s="3" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F5" s="30"/>
-      <x:c r="G5" s="20"/>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="F5" s="28"/>
+      <x:c r="G5" s="21"/>
       <x:c r="H5" s="3" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="I5" s="30"/>
-      <x:c r="J5" s="20"/>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="I5" s="28"/>
+      <x:c r="J5" s="21"/>
       <x:c r="K5" s="3" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="L5" s="30"/>
-      <x:c r="M5" s="20"/>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="L5" s="28"/>
+      <x:c r="M5" s="21"/>
     </x:row>
     <x:row r="6" spans="2:13" ht="25.5" customHeight="1">
       <x:c r="B6" s="4" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C6" s="32">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C6" s="29">
         <x:f>SUM(C5:D5,-C27:D27)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D6" s="20"/>
+      <x:c r="D6" s="21"/>
       <x:c r="E6" s="5" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="F6" s="32">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F6" s="29">
         <x:f>SUM(F5:G5,-F27:G27)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G6" s="20"/>
+      <x:c r="G6" s="21"/>
       <x:c r="H6" s="5" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="I6" s="32">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="I6" s="29">
         <x:f>SUM(I5:J5,-I27:J27)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J6" s="20"/>
+      <x:c r="J6" s="21"/>
       <x:c r="K6" s="5" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="L6" s="32">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="L6" s="29">
         <x:f>SUM(L5:M5,-L27:M27)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M6" s="20"/>
+      <x:c r="M6" s="21"/>
     </x:row>
     <x:row r="7" spans="2:13" ht="25.5" customHeight="1">
-      <x:c r="B7" s="33" t="s">
+      <x:c r="B7" s="30" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C7" s="31"/>
+      <x:c r="D7" s="21"/>
+      <x:c r="E7" s="30" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F7" s="31"/>
+      <x:c r="G7" s="21"/>
+      <x:c r="H7" s="30" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="I7" s="31"/>
+      <x:c r="J7" s="21"/>
+      <x:c r="K7" s="30" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C7" s="29"/>
-      <x:c r="D7" s="20"/>
-      <x:c r="E7" s="33" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="F7" s="29"/>
-      <x:c r="G7" s="20"/>
-      <x:c r="H7" s="33" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="I7" s="29"/>
-      <x:c r="J7" s="20"/>
-      <x:c r="K7" s="33" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="L7" s="29"/>
-      <x:c r="M7" s="20"/>
+      <x:c r="L7" s="31"/>
+      <x:c r="M7" s="21"/>
     </x:row>
     <x:row r="8" spans="2:13" ht="25.5" customHeight="1">
       <x:c r="B8" s="6" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C8" s="7" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D8" s="8" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C8" s="7" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D8" s="8" t="s">
-        <x:v>13</x:v>
-      </x:c>
       <x:c r="E8" s="6" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="F8" s="7" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G8" s="8" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="F8" s="7" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G8" s="8" t="s">
-        <x:v>13</x:v>
-      </x:c>
       <x:c r="H8" s="6" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I8" s="7" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="J8" s="8" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="I8" s="7" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="J8" s="8" t="s">
-        <x:v>13</x:v>
-      </x:c>
       <x:c r="K8" s="6" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="L8" s="7" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="M8" s="8" t="s">
         <x:v>10</x:v>
-      </x:c>
-      <x:c r="L8" s="7" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="M8" s="8" t="s">
-        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="2:13" ht="25.5" customHeight="1">
@@ -25718,37 +25700,37 @@
     <x:row r="27" spans="1:20" ht="25.5" customHeight="1">
       <x:c r="A27" s="15"/>
       <x:c r="B27" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C27" s="34">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C27" s="32">
         <x:f>SUM(D9:D26)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D27" s="20"/>
+      <x:c r="D27" s="21"/>
       <x:c r="E27" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="F27" s="34">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="F27" s="32">
         <x:f>SUM(G9:G26)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G27" s="20"/>
+      <x:c r="G27" s="21"/>
       <x:c r="H27" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="I27" s="34">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="I27" s="32">
         <x:f>SUM(J9:J26)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J27" s="20"/>
+      <x:c r="J27" s="21"/>
       <x:c r="K27" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="L27" s="34">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="L27" s="32">
         <x:f>SUM(M9:M26)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M27" s="20"/>
+      <x:c r="M27" s="21"/>
       <x:c r="N27" s="15"/>
       <x:c r="O27" s="15"/>
       <x:c r="P27" s="15"/>
@@ -25763,13 +25745,13 @@
     <x:row r="29" spans="1:23" ht="25.5" customHeight="1">
       <x:c r="A29" s="17"/>
       <x:c r="B29" s="6" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C29" s="36">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C29" s="33">
         <x:f>SUM(C27:D27,F27:G27,I27:J27,L27:M27)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D29" s="20"/>
+      <x:c r="D29" s="21"/>
       <x:c r="E29" s="17"/>
       <x:c r="F29" s="17"/>
       <x:c r="G29" s="17"/>
@@ -28734,7 +28716,7 @@
     <x:mergeCell ref="L27:M27"/>
     <x:mergeCell ref="C29:D29"/>
   </x:mergeCells>
-  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51152777671813964844" footer="0.51152777671813964844"/>
+  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51138889789581298828" footer="0.51138889789581298828"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="0" verticalDpi="0" copies="1"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="1" alignWithMargins="1"/>
 </x:worksheet>
@@ -28762,30 +28744,30 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="2:7" ht="25.5" customHeight="1">
-      <x:c r="B1" s="19"/>
-      <x:c r="C1" s="20"/>
+      <x:c r="B1" s="34"/>
+      <x:c r="C1" s="21"/>
       <x:c r="D1" s="1"/>
       <x:c r="E1" s="2" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F1" s="21"/>
-      <x:c r="G1" s="20"/>
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F1" s="20"/>
+      <x:c r="G1" s="21"/>
     </x:row>
     <x:row r="2" spans="2:9" ht="25.5" customHeight="1">
       <x:c r="B2" s="22" t="s">
-        <x:v>7</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C2" s="24">
         <x:f>SUM(F1:G1,-C29:D29)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D2" s="25"/>
-      <x:c r="F2" s="28" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="29"/>
-      <x:c r="H2" s="29"/>
-      <x:c r="I2" s="20"/>
+      <x:c r="F2" s="35" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G2" s="31"/>
+      <x:c r="H2" s="31"/>
+      <x:c r="I2" s="21"/>
     </x:row>
     <x:row r="3" spans="2:4" ht="10.5" customHeight="1">
       <x:c r="B3" s="23"/>
@@ -28797,118 +28779,118 @@
     </x:row>
     <x:row r="5" spans="2:13" ht="25.5" customHeight="1">
       <x:c r="B5" s="2" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C5" s="30"/>
-      <x:c r="D5" s="20"/>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C5" s="28"/>
+      <x:c r="D5" s="21"/>
       <x:c r="E5" s="3" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F5" s="30"/>
-      <x:c r="G5" s="20"/>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="F5" s="28"/>
+      <x:c r="G5" s="21"/>
       <x:c r="H5" s="3" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="I5" s="30"/>
-      <x:c r="J5" s="20"/>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="I5" s="28"/>
+      <x:c r="J5" s="21"/>
       <x:c r="K5" s="3" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="L5" s="30"/>
-      <x:c r="M5" s="20"/>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="L5" s="28"/>
+      <x:c r="M5" s="21"/>
     </x:row>
     <x:row r="6" spans="2:13" ht="25.5" customHeight="1">
       <x:c r="B6" s="4" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C6" s="32">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C6" s="29">
         <x:f>SUM(C5:D5,-C27:D27)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D6" s="20"/>
+      <x:c r="D6" s="21"/>
       <x:c r="E6" s="5" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="F6" s="32">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F6" s="29">
         <x:f>SUM(F5:G5,-F27:G27)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G6" s="20"/>
+      <x:c r="G6" s="21"/>
       <x:c r="H6" s="5" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="I6" s="32">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="I6" s="29">
         <x:f>SUM(I5:J5,-I27:J27)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J6" s="20"/>
+      <x:c r="J6" s="21"/>
       <x:c r="K6" s="5" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="L6" s="32">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="L6" s="29">
         <x:f>SUM(L5:M5,-L27:M27)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M6" s="20"/>
+      <x:c r="M6" s="21"/>
     </x:row>
     <x:row r="7" spans="2:13" ht="25.5" customHeight="1">
-      <x:c r="B7" s="33" t="s">
+      <x:c r="B7" s="30" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C7" s="31"/>
+      <x:c r="D7" s="21"/>
+      <x:c r="E7" s="30" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F7" s="31"/>
+      <x:c r="G7" s="21"/>
+      <x:c r="H7" s="30" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="I7" s="31"/>
+      <x:c r="J7" s="21"/>
+      <x:c r="K7" s="30" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C7" s="29"/>
-      <x:c r="D7" s="20"/>
-      <x:c r="E7" s="33" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="F7" s="29"/>
-      <x:c r="G7" s="20"/>
-      <x:c r="H7" s="33" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="I7" s="29"/>
-      <x:c r="J7" s="20"/>
-      <x:c r="K7" s="33" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="L7" s="29"/>
-      <x:c r="M7" s="20"/>
+      <x:c r="L7" s="31"/>
+      <x:c r="M7" s="21"/>
     </x:row>
     <x:row r="8" spans="2:13" ht="25.5" customHeight="1">
       <x:c r="B8" s="6" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C8" s="7" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D8" s="8" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C8" s="7" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D8" s="8" t="s">
-        <x:v>13</x:v>
-      </x:c>
       <x:c r="E8" s="6" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="F8" s="7" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G8" s="8" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="F8" s="7" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G8" s="8" t="s">
-        <x:v>13</x:v>
-      </x:c>
       <x:c r="H8" s="6" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I8" s="7" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="J8" s="8" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="I8" s="7" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="J8" s="8" t="s">
-        <x:v>13</x:v>
-      </x:c>
       <x:c r="K8" s="6" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="L8" s="7" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="M8" s="8" t="s">
         <x:v>10</x:v>
-      </x:c>
-      <x:c r="L8" s="7" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="M8" s="8" t="s">
-        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="2:13" ht="25.5" customHeight="1">
@@ -29166,37 +29148,37 @@
     <x:row r="27" spans="1:20" ht="25.5" customHeight="1">
       <x:c r="A27" s="15"/>
       <x:c r="B27" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C27" s="34">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C27" s="32">
         <x:f>SUM(D9:D26)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D27" s="20"/>
+      <x:c r="D27" s="21"/>
       <x:c r="E27" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="F27" s="34">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="F27" s="32">
         <x:f>SUM(G9:G26)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G27" s="20"/>
+      <x:c r="G27" s="21"/>
       <x:c r="H27" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="I27" s="34">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="I27" s="32">
         <x:f>SUM(J9:J26)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J27" s="20"/>
+      <x:c r="J27" s="21"/>
       <x:c r="K27" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="L27" s="34">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="L27" s="32">
         <x:f>SUM(M9:M26)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M27" s="20"/>
+      <x:c r="M27" s="21"/>
       <x:c r="N27" s="15"/>
       <x:c r="O27" s="15"/>
       <x:c r="P27" s="15"/>
@@ -29211,13 +29193,13 @@
     <x:row r="29" spans="1:23" ht="25.5" customHeight="1">
       <x:c r="A29" s="17"/>
       <x:c r="B29" s="6" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C29" s="36">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C29" s="33">
         <x:f>SUM(C27:D27,F27:G27,I27:J27,L27:M27)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D29" s="20"/>
+      <x:c r="D29" s="21"/>
       <x:c r="E29" s="17"/>
       <x:c r="F29" s="17"/>
       <x:c r="G29" s="17"/>
@@ -32182,7 +32164,7 @@
     <x:mergeCell ref="L27:M27"/>
     <x:mergeCell ref="C29:D29"/>
   </x:mergeCells>
-  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51152777671813964844" footer="0.51152777671813964844"/>
+  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51138889789581298828" footer="0.51138889789581298828"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="0" verticalDpi="0" copies="1"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="1" alignWithMargins="1"/>
 </x:worksheet>
@@ -32210,30 +32192,30 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="2:7" ht="25.5" customHeight="1">
-      <x:c r="B1" s="19"/>
-      <x:c r="C1" s="20"/>
+      <x:c r="B1" s="34"/>
+      <x:c r="C1" s="21"/>
       <x:c r="D1" s="1"/>
       <x:c r="E1" s="2" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F1" s="21"/>
-      <x:c r="G1" s="20"/>
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F1" s="20"/>
+      <x:c r="G1" s="21"/>
     </x:row>
     <x:row r="2" spans="2:9" ht="25.5" customHeight="1">
       <x:c r="B2" s="22" t="s">
-        <x:v>7</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C2" s="24">
         <x:f>SUM(F1:G1,-C29:D29)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D2" s="25"/>
-      <x:c r="F2" s="28" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="29"/>
-      <x:c r="H2" s="29"/>
-      <x:c r="I2" s="20"/>
+      <x:c r="F2" s="35" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G2" s="31"/>
+      <x:c r="H2" s="31"/>
+      <x:c r="I2" s="21"/>
     </x:row>
     <x:row r="3" spans="2:4" ht="10.5" customHeight="1">
       <x:c r="B3" s="23"/>
@@ -32245,118 +32227,118 @@
     </x:row>
     <x:row r="5" spans="2:13" ht="25.5" customHeight="1">
       <x:c r="B5" s="2" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C5" s="30"/>
-      <x:c r="D5" s="20"/>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C5" s="28"/>
+      <x:c r="D5" s="21"/>
       <x:c r="E5" s="3" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F5" s="30"/>
-      <x:c r="G5" s="20"/>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="F5" s="28"/>
+      <x:c r="G5" s="21"/>
       <x:c r="H5" s="3" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="I5" s="30"/>
-      <x:c r="J5" s="20"/>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="I5" s="28"/>
+      <x:c r="J5" s="21"/>
       <x:c r="K5" s="3" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="L5" s="30"/>
-      <x:c r="M5" s="20"/>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="L5" s="28"/>
+      <x:c r="M5" s="21"/>
     </x:row>
     <x:row r="6" spans="2:13" ht="25.5" customHeight="1">
       <x:c r="B6" s="4" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C6" s="32">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C6" s="29">
         <x:f>SUM(C5:D5,-C27:D27)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D6" s="20"/>
+      <x:c r="D6" s="21"/>
       <x:c r="E6" s="5" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="F6" s="32">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F6" s="29">
         <x:f>SUM(F5:G5,-F27:G27)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G6" s="20"/>
+      <x:c r="G6" s="21"/>
       <x:c r="H6" s="5" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="I6" s="32">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="I6" s="29">
         <x:f>SUM(I5:J5,-I27:J27)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J6" s="20"/>
+      <x:c r="J6" s="21"/>
       <x:c r="K6" s="5" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="L6" s="32">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="L6" s="29">
         <x:f>SUM(L5:M5,-L27:M27)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M6" s="20"/>
+      <x:c r="M6" s="21"/>
     </x:row>
     <x:row r="7" spans="2:13" ht="25.5" customHeight="1">
-      <x:c r="B7" s="33" t="s">
+      <x:c r="B7" s="30" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C7" s="31"/>
+      <x:c r="D7" s="21"/>
+      <x:c r="E7" s="30" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F7" s="31"/>
+      <x:c r="G7" s="21"/>
+      <x:c r="H7" s="30" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="I7" s="31"/>
+      <x:c r="J7" s="21"/>
+      <x:c r="K7" s="30" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C7" s="29"/>
-      <x:c r="D7" s="20"/>
-      <x:c r="E7" s="33" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="F7" s="29"/>
-      <x:c r="G7" s="20"/>
-      <x:c r="H7" s="33" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="I7" s="29"/>
-      <x:c r="J7" s="20"/>
-      <x:c r="K7" s="33" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="L7" s="29"/>
-      <x:c r="M7" s="20"/>
+      <x:c r="L7" s="31"/>
+      <x:c r="M7" s="21"/>
     </x:row>
     <x:row r="8" spans="2:13" ht="25.5" customHeight="1">
       <x:c r="B8" s="6" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C8" s="7" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D8" s="8" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C8" s="7" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D8" s="8" t="s">
-        <x:v>13</x:v>
-      </x:c>
       <x:c r="E8" s="6" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="F8" s="7" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G8" s="8" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="F8" s="7" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G8" s="8" t="s">
-        <x:v>13</x:v>
-      </x:c>
       <x:c r="H8" s="6" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I8" s="7" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="J8" s="8" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="I8" s="7" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="J8" s="8" t="s">
-        <x:v>13</x:v>
-      </x:c>
       <x:c r="K8" s="6" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="L8" s="7" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="M8" s="8" t="s">
         <x:v>10</x:v>
-      </x:c>
-      <x:c r="L8" s="7" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="M8" s="8" t="s">
-        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="2:13" ht="25.5" customHeight="1">
@@ -32614,37 +32596,37 @@
     <x:row r="27" spans="1:20" ht="25.5" customHeight="1">
       <x:c r="A27" s="15"/>
       <x:c r="B27" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C27" s="34">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C27" s="32">
         <x:f>SUM(D9:D26)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D27" s="20"/>
+      <x:c r="D27" s="21"/>
       <x:c r="E27" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="F27" s="34">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="F27" s="32">
         <x:f>SUM(G9:G26)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G27" s="20"/>
+      <x:c r="G27" s="21"/>
       <x:c r="H27" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="I27" s="34">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="I27" s="32">
         <x:f>SUM(J9:J26)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J27" s="20"/>
+      <x:c r="J27" s="21"/>
       <x:c r="K27" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="L27" s="34">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="L27" s="32">
         <x:f>SUM(M9:M26)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M27" s="20"/>
+      <x:c r="M27" s="21"/>
       <x:c r="N27" s="15"/>
       <x:c r="O27" s="15"/>
       <x:c r="P27" s="15"/>
@@ -32659,13 +32641,13 @@
     <x:row r="29" spans="1:23" ht="25.5" customHeight="1">
       <x:c r="A29" s="17"/>
       <x:c r="B29" s="6" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C29" s="36">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C29" s="33">
         <x:f>SUM(C27:D27,F27:G27,I27:J27,L27:M27)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D29" s="20"/>
+      <x:c r="D29" s="21"/>
       <x:c r="E29" s="17"/>
       <x:c r="F29" s="17"/>
       <x:c r="G29" s="17"/>
@@ -35630,7 +35612,7 @@
     <x:mergeCell ref="L27:M27"/>
     <x:mergeCell ref="C29:D29"/>
   </x:mergeCells>
-  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51152777671813964844" footer="0.51152777671813964844"/>
+  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51138889789581298828" footer="0.51138889789581298828"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="0" verticalDpi="0" copies="1"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="1" alignWithMargins="1"/>
 </x:worksheet>
@@ -35658,30 +35640,30 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="2:7" ht="25.5" customHeight="1">
-      <x:c r="B1" s="19"/>
-      <x:c r="C1" s="20"/>
+      <x:c r="B1" s="34"/>
+      <x:c r="C1" s="21"/>
       <x:c r="D1" s="1"/>
       <x:c r="E1" s="2" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F1" s="21"/>
-      <x:c r="G1" s="20"/>
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F1" s="20"/>
+      <x:c r="G1" s="21"/>
     </x:row>
     <x:row r="2" spans="2:9" ht="25.5" customHeight="1">
       <x:c r="B2" s="22" t="s">
-        <x:v>7</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C2" s="24">
         <x:f>SUM(F1:G1,-C29:D29)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D2" s="25"/>
-      <x:c r="F2" s="28" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="29"/>
-      <x:c r="H2" s="29"/>
-      <x:c r="I2" s="20"/>
+      <x:c r="F2" s="35" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G2" s="31"/>
+      <x:c r="H2" s="31"/>
+      <x:c r="I2" s="21"/>
     </x:row>
     <x:row r="3" spans="2:4" ht="10.5" customHeight="1">
       <x:c r="B3" s="23"/>
@@ -35693,118 +35675,118 @@
     </x:row>
     <x:row r="5" spans="2:13" ht="25.5" customHeight="1">
       <x:c r="B5" s="2" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C5" s="30"/>
-      <x:c r="D5" s="20"/>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C5" s="28"/>
+      <x:c r="D5" s="21"/>
       <x:c r="E5" s="3" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F5" s="30"/>
-      <x:c r="G5" s="20"/>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="F5" s="28"/>
+      <x:c r="G5" s="21"/>
       <x:c r="H5" s="3" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="I5" s="30"/>
-      <x:c r="J5" s="20"/>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="I5" s="28"/>
+      <x:c r="J5" s="21"/>
       <x:c r="K5" s="3" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="L5" s="30"/>
-      <x:c r="M5" s="20"/>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="L5" s="28"/>
+      <x:c r="M5" s="21"/>
     </x:row>
     <x:row r="6" spans="2:13" ht="25.5" customHeight="1">
       <x:c r="B6" s="4" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C6" s="32">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C6" s="29">
         <x:f>SUM(C5:D5,-C27:D27)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D6" s="20"/>
+      <x:c r="D6" s="21"/>
       <x:c r="E6" s="5" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="F6" s="32">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F6" s="29">
         <x:f>SUM(F5:G5,-F27:G27)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G6" s="20"/>
+      <x:c r="G6" s="21"/>
       <x:c r="H6" s="5" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="I6" s="32">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="I6" s="29">
         <x:f>SUM(I5:J5,-I27:J27)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J6" s="20"/>
+      <x:c r="J6" s="21"/>
       <x:c r="K6" s="5" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="L6" s="32">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="L6" s="29">
         <x:f>SUM(L5:M5,-L27:M27)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M6" s="20"/>
+      <x:c r="M6" s="21"/>
     </x:row>
     <x:row r="7" spans="2:13" ht="25.5" customHeight="1">
-      <x:c r="B7" s="33" t="s">
+      <x:c r="B7" s="30" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C7" s="31"/>
+      <x:c r="D7" s="21"/>
+      <x:c r="E7" s="30" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F7" s="31"/>
+      <x:c r="G7" s="21"/>
+      <x:c r="H7" s="30" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="I7" s="31"/>
+      <x:c r="J7" s="21"/>
+      <x:c r="K7" s="30" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C7" s="29"/>
-      <x:c r="D7" s="20"/>
-      <x:c r="E7" s="33" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="F7" s="29"/>
-      <x:c r="G7" s="20"/>
-      <x:c r="H7" s="33" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="I7" s="29"/>
-      <x:c r="J7" s="20"/>
-      <x:c r="K7" s="33" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="L7" s="29"/>
-      <x:c r="M7" s="20"/>
+      <x:c r="L7" s="31"/>
+      <x:c r="M7" s="21"/>
     </x:row>
     <x:row r="8" spans="2:13" ht="25.5" customHeight="1">
       <x:c r="B8" s="6" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C8" s="7" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D8" s="8" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C8" s="7" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D8" s="8" t="s">
-        <x:v>13</x:v>
-      </x:c>
       <x:c r="E8" s="6" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="F8" s="7" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G8" s="8" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="F8" s="7" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G8" s="8" t="s">
-        <x:v>13</x:v>
-      </x:c>
       <x:c r="H8" s="6" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I8" s="7" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="J8" s="8" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="I8" s="7" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="J8" s="8" t="s">
-        <x:v>13</x:v>
-      </x:c>
       <x:c r="K8" s="6" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="L8" s="7" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="M8" s="8" t="s">
         <x:v>10</x:v>
-      </x:c>
-      <x:c r="L8" s="7" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="M8" s="8" t="s">
-        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="2:13" ht="25.5" customHeight="1">
@@ -36062,37 +36044,37 @@
     <x:row r="27" spans="1:20" ht="25.5" customHeight="1">
       <x:c r="A27" s="15"/>
       <x:c r="B27" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C27" s="34">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C27" s="32">
         <x:f>SUM(D9:D26)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D27" s="20"/>
+      <x:c r="D27" s="21"/>
       <x:c r="E27" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="F27" s="34">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="F27" s="32">
         <x:f>SUM(G9:G26)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G27" s="20"/>
+      <x:c r="G27" s="21"/>
       <x:c r="H27" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="I27" s="34">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="I27" s="32">
         <x:f>SUM(J9:J26)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J27" s="20"/>
+      <x:c r="J27" s="21"/>
       <x:c r="K27" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="L27" s="34">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="L27" s="32">
         <x:f>SUM(M9:M26)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M27" s="20"/>
+      <x:c r="M27" s="21"/>
       <x:c r="N27" s="15"/>
       <x:c r="O27" s="15"/>
       <x:c r="P27" s="15"/>
@@ -36107,13 +36089,13 @@
     <x:row r="29" spans="1:23" ht="25.5" customHeight="1">
       <x:c r="A29" s="17"/>
       <x:c r="B29" s="6" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C29" s="36">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C29" s="33">
         <x:f>SUM(C27:D27,F27:G27,I27:J27,L27:M27)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D29" s="20"/>
+      <x:c r="D29" s="21"/>
       <x:c r="E29" s="17"/>
       <x:c r="F29" s="17"/>
       <x:c r="G29" s="17"/>
@@ -39078,7 +39060,7 @@
     <x:mergeCell ref="L27:M27"/>
     <x:mergeCell ref="C29:D29"/>
   </x:mergeCells>
-  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51152777671813964844" footer="0.51152777671813964844"/>
+  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51138889789581298828" footer="0.51138889789581298828"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="0" verticalDpi="0" copies="1"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="1" alignWithMargins="1"/>
 </x:worksheet>
@@ -39106,30 +39088,30 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="2:7" ht="25.5" customHeight="1">
-      <x:c r="B1" s="19"/>
-      <x:c r="C1" s="20"/>
+      <x:c r="B1" s="34"/>
+      <x:c r="C1" s="21"/>
       <x:c r="D1" s="1"/>
       <x:c r="E1" s="2" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F1" s="21"/>
-      <x:c r="G1" s="20"/>
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F1" s="20"/>
+      <x:c r="G1" s="21"/>
     </x:row>
     <x:row r="2" spans="2:9" ht="25.5" customHeight="1">
       <x:c r="B2" s="22" t="s">
-        <x:v>7</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C2" s="24">
         <x:f>SUM(F1:G1,-C29:D29)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D2" s="25"/>
-      <x:c r="F2" s="28" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="29"/>
-      <x:c r="H2" s="29"/>
-      <x:c r="I2" s="20"/>
+      <x:c r="F2" s="35" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G2" s="31"/>
+      <x:c r="H2" s="31"/>
+      <x:c r="I2" s="21"/>
     </x:row>
     <x:row r="3" spans="2:4" ht="10.5" customHeight="1">
       <x:c r="B3" s="23"/>
@@ -39141,118 +39123,118 @@
     </x:row>
     <x:row r="5" spans="2:13" ht="25.5" customHeight="1">
       <x:c r="B5" s="2" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C5" s="30"/>
-      <x:c r="D5" s="20"/>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C5" s="28"/>
+      <x:c r="D5" s="21"/>
       <x:c r="E5" s="3" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F5" s="30"/>
-      <x:c r="G5" s="20"/>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="F5" s="28"/>
+      <x:c r="G5" s="21"/>
       <x:c r="H5" s="3" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="I5" s="30"/>
-      <x:c r="J5" s="20"/>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="I5" s="28"/>
+      <x:c r="J5" s="21"/>
       <x:c r="K5" s="3" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="L5" s="30"/>
-      <x:c r="M5" s="20"/>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="L5" s="28"/>
+      <x:c r="M5" s="21"/>
     </x:row>
     <x:row r="6" spans="2:13" ht="25.5" customHeight="1">
       <x:c r="B6" s="4" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C6" s="32">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C6" s="29">
         <x:f>SUM(C5:D5,-C27:D27)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D6" s="20"/>
+      <x:c r="D6" s="21"/>
       <x:c r="E6" s="5" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="F6" s="32">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F6" s="29">
         <x:f>SUM(F5:G5,-F27:G27)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G6" s="20"/>
+      <x:c r="G6" s="21"/>
       <x:c r="H6" s="5" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="I6" s="32">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="I6" s="29">
         <x:f>SUM(I5:J5,-I27:J27)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J6" s="20"/>
+      <x:c r="J6" s="21"/>
       <x:c r="K6" s="5" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="L6" s="32">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="L6" s="29">
         <x:f>SUM(L5:M5,-L27:M27)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M6" s="20"/>
+      <x:c r="M6" s="21"/>
     </x:row>
     <x:row r="7" spans="2:13" ht="25.5" customHeight="1">
-      <x:c r="B7" s="33" t="s">
+      <x:c r="B7" s="30" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C7" s="31"/>
+      <x:c r="D7" s="21"/>
+      <x:c r="E7" s="30" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F7" s="31"/>
+      <x:c r="G7" s="21"/>
+      <x:c r="H7" s="30" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="I7" s="31"/>
+      <x:c r="J7" s="21"/>
+      <x:c r="K7" s="30" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C7" s="29"/>
-      <x:c r="D7" s="20"/>
-      <x:c r="E7" s="33" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="F7" s="29"/>
-      <x:c r="G7" s="20"/>
-      <x:c r="H7" s="33" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="I7" s="29"/>
-      <x:c r="J7" s="20"/>
-      <x:c r="K7" s="33" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="L7" s="29"/>
-      <x:c r="M7" s="20"/>
+      <x:c r="L7" s="31"/>
+      <x:c r="M7" s="21"/>
     </x:row>
     <x:row r="8" spans="2:13" ht="25.5" customHeight="1">
       <x:c r="B8" s="6" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C8" s="7" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D8" s="8" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C8" s="7" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D8" s="8" t="s">
-        <x:v>13</x:v>
-      </x:c>
       <x:c r="E8" s="6" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="F8" s="7" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G8" s="8" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="F8" s="7" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G8" s="8" t="s">
-        <x:v>13</x:v>
-      </x:c>
       <x:c r="H8" s="6" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I8" s="7" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="J8" s="8" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="I8" s="7" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="J8" s="8" t="s">
-        <x:v>13</x:v>
-      </x:c>
       <x:c r="K8" s="6" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="L8" s="7" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="M8" s="8" t="s">
         <x:v>10</x:v>
-      </x:c>
-      <x:c r="L8" s="7" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="M8" s="8" t="s">
-        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="2:13" ht="25.5" customHeight="1">
@@ -39510,37 +39492,37 @@
     <x:row r="27" spans="1:20" ht="25.5" customHeight="1">
       <x:c r="A27" s="15"/>
       <x:c r="B27" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C27" s="34">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C27" s="32">
         <x:f>SUM(D9:D26)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D27" s="20"/>
+      <x:c r="D27" s="21"/>
       <x:c r="E27" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="F27" s="34">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="F27" s="32">
         <x:f>SUM(G9:G26)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G27" s="20"/>
+      <x:c r="G27" s="21"/>
       <x:c r="H27" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="I27" s="34">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="I27" s="32">
         <x:f>SUM(J9:J26)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J27" s="20"/>
+      <x:c r="J27" s="21"/>
       <x:c r="K27" s="16" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="L27" s="34">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="L27" s="32">
         <x:f>SUM(M9:M26)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M27" s="20"/>
+      <x:c r="M27" s="21"/>
       <x:c r="N27" s="15"/>
       <x:c r="O27" s="15"/>
       <x:c r="P27" s="15"/>
@@ -39555,13 +39537,13 @@
     <x:row r="29" spans="1:23" ht="25.5" customHeight="1">
       <x:c r="A29" s="17"/>
       <x:c r="B29" s="6" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C29" s="36">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C29" s="33">
         <x:f>SUM(C27:D27,F27:G27,I27:J27,L27:M27)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D29" s="20"/>
+      <x:c r="D29" s="21"/>
       <x:c r="E29" s="17"/>
       <x:c r="F29" s="17"/>
       <x:c r="G29" s="17"/>
@@ -42526,7 +42508,7 @@
     <x:mergeCell ref="L27:M27"/>
     <x:mergeCell ref="C29:D29"/>
   </x:mergeCells>
-  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51152777671813964844" footer="0.51152777671813964844"/>
+  <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51138889789581298828" footer="0.51138889789581298828"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="0" verticalDpi="0" copies="1"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="1" alignWithMargins="1"/>
 </x:worksheet>

--- a/PIP_장부.xlsx
+++ b/PIP_장부.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="25380" windowHeight="11100" tabRatio="500"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="12540" windowHeight="11060" tabRatio="500"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="1" sheetId="1" r:id="rId4"/>
@@ -32,40 +32,13 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="24">
   <x:si>
-    <x:t>UI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>enemy</x:t>
-  </x:si>
-  <x:si>
-    <x:t>지원금</x:t>
-  </x:si>
-  <x:si>
-    <x:t>잔액</x:t>
-  </x:si>
-  <x:si>
-    <x:t>내역</x:t>
-  </x:si>
-  <x:si>
     <x:t>남은돈</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그 외</x:t>
-  </x:si>
-  <x:si>
-    <x:t>합계</x:t>
-  </x:si>
-  <x:si>
-    <x:t>월/일</x:t>
-  </x:si>
-  <x:si>
-    <x:t>교통비</x:t>
   </x:si>
   <x:si>
     <x:t>지출액</x:t>
   </x:si>
   <x:si>
-    <x:t>식비</x:t>
+    <x:t>그 외</x:t>
   </x:si>
   <x:si>
     <x:t>생활비</x:t>
@@ -74,34 +47,61 @@
     <x:t>예산</x:t>
   </x:si>
   <x:si>
+    <x:t>월/일</x:t>
+  </x:si>
+  <x:si>
+    <x:t>식비</x:t>
+  </x:si>
+  <x:si>
+    <x:t>합계</x:t>
+  </x:si>
+  <x:si>
+    <x:t>교통비</x:t>
+  </x:si>
+  <x:si>
+    <x:t>내역</x:t>
+  </x:si>
+  <x:si>
+    <x:t>npc bundle</x:t>
+  </x:si>
+  <x:si>
     <x:t>ddr5 램 x2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>weapon pack</x:t>
+  </x:si>
+  <x:si>
+    <x:t>enemy bundle</x:t>
   </x:si>
   <x:si>
     <x:t>변동지출: 소비성 지출(구독료도 포함!)</x:t>
   </x:si>
   <x:si>
+    <x:t>enemy</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TREE</x:t>
+  </x:si>
+  <x:si>
     <x:t>교육/문화비</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIELD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>남은 예산</x:t>
   </x:si>
   <x:si>
     <x:t>총 지출</x:t>
   </x:si>
   <x:si>
-    <x:t>남은 예산</x:t>
+    <x:t>잔액</x:t>
   </x:si>
   <x:si>
-    <x:t>npc bundle</x:t>
+    <x:t>UI</x:t>
   </x:si>
   <x:si>
-    <x:t>FIELD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>enemy bundle</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TREE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>weapon pack</x:t>
+    <x:t>지원금</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -279,6 +279,26 @@
       <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
         <x:font hs:extension="1">
           <x:name val="Arial"/>
+          <x:sz val="12"/>
+          <x:color rgb="ff000000"/>
+          <hs:size val="100"/>
+          <hs:ratio val="100"/>
+          <hs:spacing val="0"/>
+          <hs:offset val="0"/>
+        </x:font>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:font>
+          <x:name val="Arial"/>
+          <x:sz val="12"/>
+          <x:color rgb="ff000000"/>
+        </x:font>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:font hs:extension="1">
+          <x:name val="Arial"/>
           <x:sz val="11"/>
           <x:color rgb="ffff0000"/>
           <hs:size val="100"/>
@@ -292,26 +312,6 @@
           <x:name val="Arial"/>
           <x:sz val="11"/>
           <x:color rgb="ffff0000"/>
-        </x:font>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:font hs:extension="1">
-          <x:name val="Arial"/>
-          <x:sz val="12"/>
-          <x:color rgb="ff000000"/>
-          <hs:size val="100"/>
-          <hs:ratio val="100"/>
-          <hs:spacing val="0"/>
-          <hs:offset val="0"/>
-        </x:font>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:font>
-          <x:name val="Arial"/>
-          <x:sz val="12"/>
-          <x:color rgb="ff000000"/>
         </x:font>
       </mc:Fallback>
     </mc:AlternateContent>
@@ -552,7 +552,7 @@
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="36">
+  <x:cellXfs count="37">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
@@ -851,45 +851,48 @@
     </x:xf>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:xf numFmtId="164" fontId="16" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
+        <x:xf numFmtId="0" fontId="16" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
           <x:alignment horizontal="center" vertical="center"/>
           <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
         </x:xf>
       </mc:Choice>
       <mc:Fallback>
-        <x:xf numFmtId="164" fontId="16" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+        <x:xf numFmtId="0" fontId="16" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+          <x:alignment horizontal="center" vertical="center"/>
+        </x:xf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:xf numFmtId="164" fontId="17" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
+          <x:alignment horizontal="center" vertical="center"/>
+          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
+        </x:xf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:xf numFmtId="164" fontId="17" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
           <x:alignment horizontal="center" vertical="center"/>
         </x:xf>
       </mc:Fallback>
     </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:xf numFmtId="164" fontId="16" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
+        <x:xf numFmtId="164" fontId="17" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
           <x:alignment horizontal="center" vertical="center"/>
           <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
         </x:xf>
       </mc:Choice>
       <mc:Fallback>
-        <x:xf numFmtId="164" fontId="16" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+        <x:xf numFmtId="164" fontId="17" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
           <x:alignment horizontal="center" vertical="center"/>
         </x:xf>
       </mc:Fallback>
     </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:xf numFmtId="0" fontId="17" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
-          <x:alignment horizontal="center" vertical="center"/>
-          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
-        </x:xf>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:xf numFmtId="0" fontId="17" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-          <x:alignment horizontal="center" vertical="center"/>
-        </x:xf>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="general" vertical="center"/>
+    <x:xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="2">
@@ -1118,7 +1121,7 @@
   <x:sheetData>
     <x:row r="1" spans="2:4" ht="25.5" customHeight="1">
       <x:c r="B1" s="2" t="s">
-        <x:v>2</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C1" s="20">
         <x:v>1000000</x:v>
@@ -1127,7 +1130,7 @@
     </x:row>
     <x:row r="2" spans="2:9" ht="25.5" customHeight="1">
       <x:c r="B2" s="22" t="s">
-        <x:v>3</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C2" s="24">
         <x:f>SUM(C1:D1,-C29:D29)</x:f>
@@ -1150,7 +1153,7 @@
     </x:row>
     <x:row r="5" spans="2:16" ht="25.5" customHeight="1">
       <x:c r="B5" s="2" t="s">
-        <x:v>13</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C5" s="28">
         <x:f>C1</x:f>
@@ -1172,7 +1175,7 @@
     </x:row>
     <x:row r="6" spans="2:16" ht="25.5" customHeight="1">
       <x:c r="B6" s="2" t="s">
-        <x:v>5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C6" s="29">
         <x:f>C2-SUM(D9:D23)</x:f>
@@ -1194,7 +1197,7 @@
     </x:row>
     <x:row r="7" spans="2:16" ht="25.5" customHeight="1">
       <x:c r="B7" s="30" t="s">
-        <x:v>11</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C7" s="31"/>
       <x:c r="D7" s="21"/>
@@ -1213,13 +1216,13 @@
     </x:row>
     <x:row r="8" spans="2:16" ht="25.5" customHeight="1">
       <x:c r="B8" s="6" t="s">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C8" s="7" t="s">
-        <x:v>4</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D8" s="8" t="s">
-        <x:v>10</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E8" s="18"/>
       <x:c r="F8" s="18"/>
@@ -1239,7 +1242,7 @@
         <x:v>45999</x:v>
       </x:c>
       <x:c r="C9" s="10" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D9" s="11">
         <x:v>401000</x:v>
@@ -1262,13 +1265,16 @@
         <x:v>46001</x:v>
       </x:c>
       <x:c r="C10" s="10" t="s">
-        <x:v>22</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D10" s="14">
         <x:v>22020</x:v>
       </x:c>
       <x:c r="E10" s="18"/>
-      <x:c r="F10" s="18"/>
+      <x:c r="F10" s="36">
+        <x:f>SUM(D9:D10)</x:f>
+        <x:v>423020</x:v>
+      </x:c>
       <x:c r="G10" s="18"/>
       <x:c r="H10" s="18"/>
       <x:c r="I10" s="18"/>
@@ -1285,13 +1291,16 @@
         <x:v>46006</x:v>
       </x:c>
       <x:c r="C11" s="10" t="s">
-        <x:v>20</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D11" s="14">
         <x:v>176870</x:v>
       </x:c>
       <x:c r="E11" s="18"/>
-      <x:c r="F11" s="18"/>
+      <x:c r="F11" s="36">
+        <x:f>SUM(D11:D16)</x:f>
+        <x:v>517290</x:v>
+      </x:c>
       <x:c r="G11" s="18"/>
       <x:c r="H11" s="18"/>
       <x:c r="I11" s="18"/>
@@ -1308,7 +1317,7 @@
         <x:v>46006</x:v>
       </x:c>
       <x:c r="C12" s="10" t="s">
-        <x:v>0</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D12" s="14">
         <x:v>14720</x:v>
@@ -1331,7 +1340,7 @@
         <x:v>46006</x:v>
       </x:c>
       <x:c r="C13" s="10" t="s">
-        <x:v>21</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D13" s="14">
         <x:v>221090</x:v>
@@ -1354,7 +1363,7 @@
         <x:v>46006</x:v>
       </x:c>
       <x:c r="C14" s="10" t="s">
-        <x:v>19</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D14" s="14">
         <x:v>38310</x:v>
@@ -1377,7 +1386,7 @@
         <x:v>46006</x:v>
       </x:c>
       <x:c r="C15" s="10" t="s">
-        <x:v>1</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D15" s="14">
         <x:v>51570</x:v>
@@ -1400,7 +1409,7 @@
         <x:v>46006</x:v>
       </x:c>
       <x:c r="C16" s="10" t="s">
-        <x:v>23</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D16" s="14">
         <x:v>14730</x:v>
@@ -4608,26 +4617,26 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="2:7" ht="25.5" customHeight="1">
-      <x:c r="B1" s="34"/>
+      <x:c r="B1" s="32"/>
       <x:c r="C1" s="21"/>
       <x:c r="D1" s="1"/>
       <x:c r="E1" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F1" s="20"/>
       <x:c r="G1" s="21"/>
     </x:row>
     <x:row r="2" spans="2:9" ht="25.5" customHeight="1">
       <x:c r="B2" s="22" t="s">
-        <x:v>3</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C2" s="24">
         <x:f>SUM(F1:G1,-C29:D29)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D2" s="25"/>
-      <x:c r="F2" s="35" t="s">
-        <x:v>15</x:v>
+      <x:c r="F2" s="33" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G2" s="31"/>
       <x:c r="H2" s="31"/>
@@ -4643,29 +4652,29 @@
     </x:row>
     <x:row r="5" spans="2:13" ht="25.5" customHeight="1">
       <x:c r="B5" s="2" t="s">
-        <x:v>13</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C5" s="28"/>
       <x:c r="D5" s="21"/>
       <x:c r="E5" s="3" t="s">
-        <x:v>13</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F5" s="28"/>
       <x:c r="G5" s="21"/>
       <x:c r="H5" s="3" t="s">
-        <x:v>13</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="I5" s="28"/>
       <x:c r="J5" s="21"/>
       <x:c r="K5" s="3" t="s">
-        <x:v>13</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="L5" s="28"/>
       <x:c r="M5" s="21"/>
     </x:row>
     <x:row r="6" spans="2:13" ht="25.5" customHeight="1">
       <x:c r="B6" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C6" s="29">
         <x:f>SUM(C5:D5,-C27:D27)</x:f>
@@ -4673,7 +4682,7 @@
       </x:c>
       <x:c r="D6" s="21"/>
       <x:c r="E6" s="5" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F6" s="29">
         <x:f>SUM(F5:G5,-F27:G27)</x:f>
@@ -4681,7 +4690,7 @@
       </x:c>
       <x:c r="G6" s="21"/>
       <x:c r="H6" s="5" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="I6" s="29">
         <x:f>SUM(I5:J5,-I27:J27)</x:f>
@@ -4689,7 +4698,7 @@
       </x:c>
       <x:c r="J6" s="21"/>
       <x:c r="K6" s="5" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="L6" s="29">
         <x:f>SUM(L5:M5,-L27:M27)</x:f>
@@ -4699,62 +4708,62 @@
     </x:row>
     <x:row r="7" spans="2:13" ht="25.5" customHeight="1">
       <x:c r="B7" s="30" t="s">
-        <x:v>11</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C7" s="31"/>
       <x:c r="D7" s="21"/>
       <x:c r="E7" s="30" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F7" s="31"/>
       <x:c r="G7" s="21"/>
       <x:c r="H7" s="30" t="s">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I7" s="31"/>
       <x:c r="J7" s="21"/>
       <x:c r="K7" s="30" t="s">
-        <x:v>6</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L7" s="31"/>
       <x:c r="M7" s="21"/>
     </x:row>
     <x:row r="8" spans="2:13" ht="25.5" customHeight="1">
       <x:c r="B8" s="6" t="s">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C8" s="7" t="s">
-        <x:v>4</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D8" s="8" t="s">
-        <x:v>10</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E8" s="6" t="s">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F8" s="7" t="s">
-        <x:v>4</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G8" s="8" t="s">
-        <x:v>10</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H8" s="6" t="s">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="I8" s="7" t="s">
-        <x:v>4</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="J8" s="8" t="s">
-        <x:v>10</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K8" s="6" t="s">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="L8" s="7" t="s">
-        <x:v>4</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="M8" s="8" t="s">
-        <x:v>10</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="2:13" ht="25.5" customHeight="1">
@@ -5014,7 +5023,7 @@
       <x:c r="B27" s="16" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C27" s="32">
+      <x:c r="C27" s="34">
         <x:f>SUM(D9:D26)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -5022,7 +5031,7 @@
       <x:c r="E27" s="16" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="F27" s="32">
+      <x:c r="F27" s="34">
         <x:f>SUM(G9:G26)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -5030,7 +5039,7 @@
       <x:c r="H27" s="16" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I27" s="32">
+      <x:c r="I27" s="34">
         <x:f>SUM(J9:J26)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -5038,7 +5047,7 @@
       <x:c r="K27" s="16" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="L27" s="32">
+      <x:c r="L27" s="34">
         <x:f>SUM(M9:M26)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -5057,9 +5066,9 @@
     <x:row r="29" spans="1:23" ht="25.5" customHeight="1">
       <x:c r="A29" s="17"/>
       <x:c r="B29" s="6" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C29" s="33">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C29" s="35">
         <x:f>SUM(C27:D27,F27:G27,I27:J27,L27:M27)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -8056,26 +8065,26 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="2:7" ht="25.5" customHeight="1">
-      <x:c r="B1" s="34"/>
+      <x:c r="B1" s="32"/>
       <x:c r="C1" s="21"/>
       <x:c r="D1" s="1"/>
       <x:c r="E1" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F1" s="20"/>
       <x:c r="G1" s="21"/>
     </x:row>
     <x:row r="2" spans="2:9" ht="25.5" customHeight="1">
       <x:c r="B2" s="22" t="s">
-        <x:v>3</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C2" s="24">
         <x:f>SUM(F1:G1,-C29:D29)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D2" s="25"/>
-      <x:c r="F2" s="35" t="s">
-        <x:v>15</x:v>
+      <x:c r="F2" s="33" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G2" s="31"/>
       <x:c r="H2" s="31"/>
@@ -8091,29 +8100,29 @@
     </x:row>
     <x:row r="5" spans="2:13" ht="25.5" customHeight="1">
       <x:c r="B5" s="2" t="s">
-        <x:v>13</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C5" s="28"/>
       <x:c r="D5" s="21"/>
       <x:c r="E5" s="3" t="s">
-        <x:v>13</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F5" s="28"/>
       <x:c r="G5" s="21"/>
       <x:c r="H5" s="3" t="s">
-        <x:v>13</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="I5" s="28"/>
       <x:c r="J5" s="21"/>
       <x:c r="K5" s="3" t="s">
-        <x:v>13</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="L5" s="28"/>
       <x:c r="M5" s="21"/>
     </x:row>
     <x:row r="6" spans="2:13" ht="25.5" customHeight="1">
       <x:c r="B6" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C6" s="29">
         <x:f>SUM(C5:D5,-C27:D27)</x:f>
@@ -8121,7 +8130,7 @@
       </x:c>
       <x:c r="D6" s="21"/>
       <x:c r="E6" s="5" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F6" s="29">
         <x:f>SUM(F5:G5,-F27:G27)</x:f>
@@ -8129,7 +8138,7 @@
       </x:c>
       <x:c r="G6" s="21"/>
       <x:c r="H6" s="5" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="I6" s="29">
         <x:f>SUM(I5:J5,-I27:J27)</x:f>
@@ -8137,7 +8146,7 @@
       </x:c>
       <x:c r="J6" s="21"/>
       <x:c r="K6" s="5" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="L6" s="29">
         <x:f>SUM(L5:M5,-L27:M27)</x:f>
@@ -8147,62 +8156,62 @@
     </x:row>
     <x:row r="7" spans="2:13" ht="25.5" customHeight="1">
       <x:c r="B7" s="30" t="s">
-        <x:v>11</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C7" s="31"/>
       <x:c r="D7" s="21"/>
       <x:c r="E7" s="30" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F7" s="31"/>
       <x:c r="G7" s="21"/>
       <x:c r="H7" s="30" t="s">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I7" s="31"/>
       <x:c r="J7" s="21"/>
       <x:c r="K7" s="30" t="s">
-        <x:v>6</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L7" s="31"/>
       <x:c r="M7" s="21"/>
     </x:row>
     <x:row r="8" spans="2:13" ht="25.5" customHeight="1">
       <x:c r="B8" s="6" t="s">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C8" s="7" t="s">
-        <x:v>4</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D8" s="8" t="s">
-        <x:v>10</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E8" s="6" t="s">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F8" s="7" t="s">
-        <x:v>4</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G8" s="8" t="s">
-        <x:v>10</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H8" s="6" t="s">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="I8" s="7" t="s">
-        <x:v>4</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="J8" s="8" t="s">
-        <x:v>10</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K8" s="6" t="s">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="L8" s="7" t="s">
-        <x:v>4</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="M8" s="8" t="s">
-        <x:v>10</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="2:13" ht="25.5" customHeight="1">
@@ -8462,7 +8471,7 @@
       <x:c r="B27" s="16" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C27" s="32">
+      <x:c r="C27" s="34">
         <x:f>SUM(D9:D26)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -8470,7 +8479,7 @@
       <x:c r="E27" s="16" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="F27" s="32">
+      <x:c r="F27" s="34">
         <x:f>SUM(G9:G26)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -8478,7 +8487,7 @@
       <x:c r="H27" s="16" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I27" s="32">
+      <x:c r="I27" s="34">
         <x:f>SUM(J9:J26)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -8486,7 +8495,7 @@
       <x:c r="K27" s="16" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="L27" s="32">
+      <x:c r="L27" s="34">
         <x:f>SUM(M9:M26)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -8505,9 +8514,9 @@
     <x:row r="29" spans="1:23" ht="25.5" customHeight="1">
       <x:c r="A29" s="17"/>
       <x:c r="B29" s="6" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C29" s="33">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C29" s="35">
         <x:f>SUM(C27:D27,F27:G27,I27:J27,L27:M27)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -11504,26 +11513,26 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="2:7" ht="25.5" customHeight="1">
-      <x:c r="B1" s="34"/>
+      <x:c r="B1" s="32"/>
       <x:c r="C1" s="21"/>
       <x:c r="D1" s="1"/>
       <x:c r="E1" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F1" s="20"/>
       <x:c r="G1" s="21"/>
     </x:row>
     <x:row r="2" spans="2:9" ht="25.5" customHeight="1">
       <x:c r="B2" s="22" t="s">
-        <x:v>3</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C2" s="24">
         <x:f>SUM(F1:G1,-C29:D29)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D2" s="25"/>
-      <x:c r="F2" s="35" t="s">
-        <x:v>15</x:v>
+      <x:c r="F2" s="33" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G2" s="31"/>
       <x:c r="H2" s="31"/>
@@ -11539,29 +11548,29 @@
     </x:row>
     <x:row r="5" spans="2:13" ht="25.5" customHeight="1">
       <x:c r="B5" s="2" t="s">
-        <x:v>13</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C5" s="28"/>
       <x:c r="D5" s="21"/>
       <x:c r="E5" s="3" t="s">
-        <x:v>13</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F5" s="28"/>
       <x:c r="G5" s="21"/>
       <x:c r="H5" s="3" t="s">
-        <x:v>13</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="I5" s="28"/>
       <x:c r="J5" s="21"/>
       <x:c r="K5" s="3" t="s">
-        <x:v>13</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="L5" s="28"/>
       <x:c r="M5" s="21"/>
     </x:row>
     <x:row r="6" spans="2:13" ht="25.5" customHeight="1">
       <x:c r="B6" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C6" s="29">
         <x:f>SUM(C5:D5,-C27:D27)</x:f>
@@ -11569,7 +11578,7 @@
       </x:c>
       <x:c r="D6" s="21"/>
       <x:c r="E6" s="5" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F6" s="29">
         <x:f>SUM(F5:G5,-F27:G27)</x:f>
@@ -11577,7 +11586,7 @@
       </x:c>
       <x:c r="G6" s="21"/>
       <x:c r="H6" s="5" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="I6" s="29">
         <x:f>SUM(I5:J5,-I27:J27)</x:f>
@@ -11585,7 +11594,7 @@
       </x:c>
       <x:c r="J6" s="21"/>
       <x:c r="K6" s="5" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="L6" s="29">
         <x:f>SUM(L5:M5,-L27:M27)</x:f>
@@ -11595,62 +11604,62 @@
     </x:row>
     <x:row r="7" spans="2:13" ht="25.5" customHeight="1">
       <x:c r="B7" s="30" t="s">
-        <x:v>11</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C7" s="31"/>
       <x:c r="D7" s="21"/>
       <x:c r="E7" s="30" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F7" s="31"/>
       <x:c r="G7" s="21"/>
       <x:c r="H7" s="30" t="s">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I7" s="31"/>
       <x:c r="J7" s="21"/>
       <x:c r="K7" s="30" t="s">
-        <x:v>6</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L7" s="31"/>
       <x:c r="M7" s="21"/>
     </x:row>
     <x:row r="8" spans="2:13" ht="25.5" customHeight="1">
       <x:c r="B8" s="6" t="s">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C8" s="7" t="s">
-        <x:v>4</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D8" s="8" t="s">
-        <x:v>10</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E8" s="6" t="s">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F8" s="7" t="s">
-        <x:v>4</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G8" s="8" t="s">
-        <x:v>10</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H8" s="6" t="s">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="I8" s="7" t="s">
-        <x:v>4</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="J8" s="8" t="s">
-        <x:v>10</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K8" s="6" t="s">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="L8" s="7" t="s">
-        <x:v>4</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="M8" s="8" t="s">
-        <x:v>10</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="2:13" ht="25.5" customHeight="1">
@@ -11910,7 +11919,7 @@
       <x:c r="B27" s="16" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C27" s="32">
+      <x:c r="C27" s="34">
         <x:f>SUM(D9:D26)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -11918,7 +11927,7 @@
       <x:c r="E27" s="16" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="F27" s="32">
+      <x:c r="F27" s="34">
         <x:f>SUM(G9:G26)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -11926,7 +11935,7 @@
       <x:c r="H27" s="16" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I27" s="32">
+      <x:c r="I27" s="34">
         <x:f>SUM(J9:J26)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -11934,7 +11943,7 @@
       <x:c r="K27" s="16" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="L27" s="32">
+      <x:c r="L27" s="34">
         <x:f>SUM(M9:M26)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -11953,9 +11962,9 @@
     <x:row r="29" spans="1:23" ht="25.5" customHeight="1">
       <x:c r="A29" s="17"/>
       <x:c r="B29" s="6" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C29" s="33">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C29" s="35">
         <x:f>SUM(C27:D27,F27:G27,I27:J27,L27:M27)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -14952,26 +14961,26 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="2:7" ht="25.5" customHeight="1">
-      <x:c r="B1" s="34"/>
+      <x:c r="B1" s="32"/>
       <x:c r="C1" s="21"/>
       <x:c r="D1" s="1"/>
       <x:c r="E1" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F1" s="20"/>
       <x:c r="G1" s="21"/>
     </x:row>
     <x:row r="2" spans="2:9" ht="25.5" customHeight="1">
       <x:c r="B2" s="22" t="s">
-        <x:v>3</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C2" s="24">
         <x:f>SUM(F1:G1,-C29:D29)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D2" s="25"/>
-      <x:c r="F2" s="35" t="s">
-        <x:v>15</x:v>
+      <x:c r="F2" s="33" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G2" s="31"/>
       <x:c r="H2" s="31"/>
@@ -14987,29 +14996,29 @@
     </x:row>
     <x:row r="5" spans="2:13" ht="25.5" customHeight="1">
       <x:c r="B5" s="2" t="s">
-        <x:v>13</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C5" s="28"/>
       <x:c r="D5" s="21"/>
       <x:c r="E5" s="3" t="s">
-        <x:v>13</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F5" s="28"/>
       <x:c r="G5" s="21"/>
       <x:c r="H5" s="3" t="s">
-        <x:v>13</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="I5" s="28"/>
       <x:c r="J5" s="21"/>
       <x:c r="K5" s="3" t="s">
-        <x:v>13</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="L5" s="28"/>
       <x:c r="M5" s="21"/>
     </x:row>
     <x:row r="6" spans="2:13" ht="25.5" customHeight="1">
       <x:c r="B6" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C6" s="29">
         <x:f>SUM(C5:D5,-C27:D27)</x:f>
@@ -15017,7 +15026,7 @@
       </x:c>
       <x:c r="D6" s="21"/>
       <x:c r="E6" s="5" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F6" s="29">
         <x:f>SUM(F5:G5,-F27:G27)</x:f>
@@ -15025,7 +15034,7 @@
       </x:c>
       <x:c r="G6" s="21"/>
       <x:c r="H6" s="5" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="I6" s="29">
         <x:f>SUM(I5:J5,-I27:J27)</x:f>
@@ -15033,7 +15042,7 @@
       </x:c>
       <x:c r="J6" s="21"/>
       <x:c r="K6" s="5" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="L6" s="29">
         <x:f>SUM(L5:M5,-L27:M27)</x:f>
@@ -15043,62 +15052,62 @@
     </x:row>
     <x:row r="7" spans="2:13" ht="25.5" customHeight="1">
       <x:c r="B7" s="30" t="s">
-        <x:v>11</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C7" s="31"/>
       <x:c r="D7" s="21"/>
       <x:c r="E7" s="30" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F7" s="31"/>
       <x:c r="G7" s="21"/>
       <x:c r="H7" s="30" t="s">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I7" s="31"/>
       <x:c r="J7" s="21"/>
       <x:c r="K7" s="30" t="s">
-        <x:v>6</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L7" s="31"/>
       <x:c r="M7" s="21"/>
     </x:row>
     <x:row r="8" spans="2:13" ht="25.5" customHeight="1">
       <x:c r="B8" s="6" t="s">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C8" s="7" t="s">
-        <x:v>4</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D8" s="8" t="s">
-        <x:v>10</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E8" s="6" t="s">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F8" s="7" t="s">
-        <x:v>4</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G8" s="8" t="s">
-        <x:v>10</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H8" s="6" t="s">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="I8" s="7" t="s">
-        <x:v>4</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="J8" s="8" t="s">
-        <x:v>10</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K8" s="6" t="s">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="L8" s="7" t="s">
-        <x:v>4</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="M8" s="8" t="s">
-        <x:v>10</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="2:13" ht="25.5" customHeight="1">
@@ -15358,7 +15367,7 @@
       <x:c r="B27" s="16" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C27" s="32">
+      <x:c r="C27" s="34">
         <x:f>SUM(D9:D26)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -15366,7 +15375,7 @@
       <x:c r="E27" s="16" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="F27" s="32">
+      <x:c r="F27" s="34">
         <x:f>SUM(G9:G26)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -15374,7 +15383,7 @@
       <x:c r="H27" s="16" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I27" s="32">
+      <x:c r="I27" s="34">
         <x:f>SUM(J9:J26)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -15382,7 +15391,7 @@
       <x:c r="K27" s="16" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="L27" s="32">
+      <x:c r="L27" s="34">
         <x:f>SUM(M9:M26)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -15401,9 +15410,9 @@
     <x:row r="29" spans="1:23" ht="25.5" customHeight="1">
       <x:c r="A29" s="17"/>
       <x:c r="B29" s="6" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C29" s="33">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C29" s="35">
         <x:f>SUM(C27:D27,F27:G27,I27:J27,L27:M27)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -18400,26 +18409,26 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="2:7" ht="25.5" customHeight="1">
-      <x:c r="B1" s="34"/>
+      <x:c r="B1" s="32"/>
       <x:c r="C1" s="21"/>
       <x:c r="D1" s="1"/>
       <x:c r="E1" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F1" s="20"/>
       <x:c r="G1" s="21"/>
     </x:row>
     <x:row r="2" spans="2:9" ht="25.5" customHeight="1">
       <x:c r="B2" s="22" t="s">
-        <x:v>3</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C2" s="24">
         <x:f>SUM(F1:G1,-C29:D29)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D2" s="25"/>
-      <x:c r="F2" s="35" t="s">
-        <x:v>15</x:v>
+      <x:c r="F2" s="33" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G2" s="31"/>
       <x:c r="H2" s="31"/>
@@ -18435,29 +18444,29 @@
     </x:row>
     <x:row r="5" spans="2:13" ht="25.5" customHeight="1">
       <x:c r="B5" s="2" t="s">
-        <x:v>13</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C5" s="28"/>
       <x:c r="D5" s="21"/>
       <x:c r="E5" s="3" t="s">
-        <x:v>13</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F5" s="28"/>
       <x:c r="G5" s="21"/>
       <x:c r="H5" s="3" t="s">
-        <x:v>13</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="I5" s="28"/>
       <x:c r="J5" s="21"/>
       <x:c r="K5" s="3" t="s">
-        <x:v>13</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="L5" s="28"/>
       <x:c r="M5" s="21"/>
     </x:row>
     <x:row r="6" spans="2:13" ht="25.5" customHeight="1">
       <x:c r="B6" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C6" s="29">
         <x:f>SUM(C5:D5,-C27:D27)</x:f>
@@ -18465,7 +18474,7 @@
       </x:c>
       <x:c r="D6" s="21"/>
       <x:c r="E6" s="5" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F6" s="29">
         <x:f>SUM(F5:G5,-F27:G27)</x:f>
@@ -18473,7 +18482,7 @@
       </x:c>
       <x:c r="G6" s="21"/>
       <x:c r="H6" s="5" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="I6" s="29">
         <x:f>SUM(I5:J5,-I27:J27)</x:f>
@@ -18481,7 +18490,7 @@
       </x:c>
       <x:c r="J6" s="21"/>
       <x:c r="K6" s="5" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="L6" s="29">
         <x:f>SUM(L5:M5,-L27:M27)</x:f>
@@ -18491,62 +18500,62 @@
     </x:row>
     <x:row r="7" spans="2:13" ht="25.5" customHeight="1">
       <x:c r="B7" s="30" t="s">
-        <x:v>11</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C7" s="31"/>
       <x:c r="D7" s="21"/>
       <x:c r="E7" s="30" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F7" s="31"/>
       <x:c r="G7" s="21"/>
       <x:c r="H7" s="30" t="s">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I7" s="31"/>
       <x:c r="J7" s="21"/>
       <x:c r="K7" s="30" t="s">
-        <x:v>6</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L7" s="31"/>
       <x:c r="M7" s="21"/>
     </x:row>
     <x:row r="8" spans="2:13" ht="25.5" customHeight="1">
       <x:c r="B8" s="6" t="s">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C8" s="7" t="s">
-        <x:v>4</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D8" s="8" t="s">
-        <x:v>10</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E8" s="6" t="s">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F8" s="7" t="s">
-        <x:v>4</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G8" s="8" t="s">
-        <x:v>10</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H8" s="6" t="s">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="I8" s="7" t="s">
-        <x:v>4</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="J8" s="8" t="s">
-        <x:v>10</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K8" s="6" t="s">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="L8" s="7" t="s">
-        <x:v>4</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="M8" s="8" t="s">
-        <x:v>10</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="2:13" ht="25.5" customHeight="1">
@@ -18806,7 +18815,7 @@
       <x:c r="B27" s="16" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C27" s="32">
+      <x:c r="C27" s="34">
         <x:f>SUM(D9:D26)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -18814,7 +18823,7 @@
       <x:c r="E27" s="16" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="F27" s="32">
+      <x:c r="F27" s="34">
         <x:f>SUM(G9:G26)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -18822,7 +18831,7 @@
       <x:c r="H27" s="16" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I27" s="32">
+      <x:c r="I27" s="34">
         <x:f>SUM(J9:J26)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -18830,7 +18839,7 @@
       <x:c r="K27" s="16" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="L27" s="32">
+      <x:c r="L27" s="34">
         <x:f>SUM(M9:M26)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -18849,9 +18858,9 @@
     <x:row r="29" spans="1:23" ht="25.5" customHeight="1">
       <x:c r="A29" s="17"/>
       <x:c r="B29" s="6" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C29" s="33">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C29" s="35">
         <x:f>SUM(C27:D27,F27:G27,I27:J27,L27:M27)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -21848,26 +21857,26 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="2:7" ht="25.5" customHeight="1">
-      <x:c r="B1" s="34"/>
+      <x:c r="B1" s="32"/>
       <x:c r="C1" s="21"/>
       <x:c r="D1" s="1"/>
       <x:c r="E1" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F1" s="20"/>
       <x:c r="G1" s="21"/>
     </x:row>
     <x:row r="2" spans="2:9" ht="25.5" customHeight="1">
       <x:c r="B2" s="22" t="s">
-        <x:v>3</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C2" s="24">
         <x:f>SUM(F1:G1,-C29:D29)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D2" s="25"/>
-      <x:c r="F2" s="35" t="s">
-        <x:v>15</x:v>
+      <x:c r="F2" s="33" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G2" s="31"/>
       <x:c r="H2" s="31"/>
@@ -21883,29 +21892,29 @@
     </x:row>
     <x:row r="5" spans="2:13" ht="25.5" customHeight="1">
       <x:c r="B5" s="2" t="s">
-        <x:v>13</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C5" s="28"/>
       <x:c r="D5" s="21"/>
       <x:c r="E5" s="3" t="s">
-        <x:v>13</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F5" s="28"/>
       <x:c r="G5" s="21"/>
       <x:c r="H5" s="3" t="s">
-        <x:v>13</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="I5" s="28"/>
       <x:c r="J5" s="21"/>
       <x:c r="K5" s="3" t="s">
-        <x:v>13</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="L5" s="28"/>
       <x:c r="M5" s="21"/>
     </x:row>
     <x:row r="6" spans="2:13" ht="25.5" customHeight="1">
       <x:c r="B6" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C6" s="29">
         <x:f>SUM(C5:D5,-C27:D27)</x:f>
@@ -21913,7 +21922,7 @@
       </x:c>
       <x:c r="D6" s="21"/>
       <x:c r="E6" s="5" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F6" s="29">
         <x:f>SUM(F5:G5,-F27:G27)</x:f>
@@ -21921,7 +21930,7 @@
       </x:c>
       <x:c r="G6" s="21"/>
       <x:c r="H6" s="5" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="I6" s="29">
         <x:f>SUM(I5:J5,-I27:J27)</x:f>
@@ -21929,7 +21938,7 @@
       </x:c>
       <x:c r="J6" s="21"/>
       <x:c r="K6" s="5" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="L6" s="29">
         <x:f>SUM(L5:M5,-L27:M27)</x:f>
@@ -21939,62 +21948,62 @@
     </x:row>
     <x:row r="7" spans="2:13" ht="25.5" customHeight="1">
       <x:c r="B7" s="30" t="s">
-        <x:v>11</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C7" s="31"/>
       <x:c r="D7" s="21"/>
       <x:c r="E7" s="30" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F7" s="31"/>
       <x:c r="G7" s="21"/>
       <x:c r="H7" s="30" t="s">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I7" s="31"/>
       <x:c r="J7" s="21"/>
       <x:c r="K7" s="30" t="s">
-        <x:v>6</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L7" s="31"/>
       <x:c r="M7" s="21"/>
     </x:row>
     <x:row r="8" spans="2:13" ht="25.5" customHeight="1">
       <x:c r="B8" s="6" t="s">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C8" s="7" t="s">
-        <x:v>4</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D8" s="8" t="s">
-        <x:v>10</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E8" s="6" t="s">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F8" s="7" t="s">
-        <x:v>4</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G8" s="8" t="s">
-        <x:v>10</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H8" s="6" t="s">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="I8" s="7" t="s">
-        <x:v>4</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="J8" s="8" t="s">
-        <x:v>10</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K8" s="6" t="s">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="L8" s="7" t="s">
-        <x:v>4</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="M8" s="8" t="s">
-        <x:v>10</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="2:13" ht="25.5" customHeight="1">
@@ -22254,7 +22263,7 @@
       <x:c r="B27" s="16" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C27" s="32">
+      <x:c r="C27" s="34">
         <x:f>SUM(D9:D26)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -22262,7 +22271,7 @@
       <x:c r="E27" s="16" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="F27" s="32">
+      <x:c r="F27" s="34">
         <x:f>SUM(G9:G26)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -22270,7 +22279,7 @@
       <x:c r="H27" s="16" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I27" s="32">
+      <x:c r="I27" s="34">
         <x:f>SUM(J9:J26)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -22278,7 +22287,7 @@
       <x:c r="K27" s="16" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="L27" s="32">
+      <x:c r="L27" s="34">
         <x:f>SUM(M9:M26)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -22297,9 +22306,9 @@
     <x:row r="29" spans="1:23" ht="25.5" customHeight="1">
       <x:c r="A29" s="17"/>
       <x:c r="B29" s="6" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C29" s="33">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C29" s="35">
         <x:f>SUM(C27:D27,F27:G27,I27:J27,L27:M27)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -25296,26 +25305,26 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="2:7" ht="25.5" customHeight="1">
-      <x:c r="B1" s="34"/>
+      <x:c r="B1" s="32"/>
       <x:c r="C1" s="21"/>
       <x:c r="D1" s="1"/>
       <x:c r="E1" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F1" s="20"/>
       <x:c r="G1" s="21"/>
     </x:row>
     <x:row r="2" spans="2:9" ht="25.5" customHeight="1">
       <x:c r="B2" s="22" t="s">
-        <x:v>3</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C2" s="24">
         <x:f>SUM(F1:G1,-C29:D29)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D2" s="25"/>
-      <x:c r="F2" s="35" t="s">
-        <x:v>15</x:v>
+      <x:c r="F2" s="33" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G2" s="31"/>
       <x:c r="H2" s="31"/>
@@ -25331,29 +25340,29 @@
     </x:row>
     <x:row r="5" spans="2:13" ht="25.5" customHeight="1">
       <x:c r="B5" s="2" t="s">
-        <x:v>13</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C5" s="28"/>
       <x:c r="D5" s="21"/>
       <x:c r="E5" s="3" t="s">
-        <x:v>13</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F5" s="28"/>
       <x:c r="G5" s="21"/>
       <x:c r="H5" s="3" t="s">
-        <x:v>13</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="I5" s="28"/>
       <x:c r="J5" s="21"/>
       <x:c r="K5" s="3" t="s">
-        <x:v>13</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="L5" s="28"/>
       <x:c r="M5" s="21"/>
     </x:row>
     <x:row r="6" spans="2:13" ht="25.5" customHeight="1">
       <x:c r="B6" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C6" s="29">
         <x:f>SUM(C5:D5,-C27:D27)</x:f>
@@ -25361,7 +25370,7 @@
       </x:c>
       <x:c r="D6" s="21"/>
       <x:c r="E6" s="5" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F6" s="29">
         <x:f>SUM(F5:G5,-F27:G27)</x:f>
@@ -25369,7 +25378,7 @@
       </x:c>
       <x:c r="G6" s="21"/>
       <x:c r="H6" s="5" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="I6" s="29">
         <x:f>SUM(I5:J5,-I27:J27)</x:f>
@@ -25377,7 +25386,7 @@
       </x:c>
       <x:c r="J6" s="21"/>
       <x:c r="K6" s="5" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="L6" s="29">
         <x:f>SUM(L5:M5,-L27:M27)</x:f>
@@ -25387,62 +25396,62 @@
     </x:row>
     <x:row r="7" spans="2:13" ht="25.5" customHeight="1">
       <x:c r="B7" s="30" t="s">
-        <x:v>11</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C7" s="31"/>
       <x:c r="D7" s="21"/>
       <x:c r="E7" s="30" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F7" s="31"/>
       <x:c r="G7" s="21"/>
       <x:c r="H7" s="30" t="s">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I7" s="31"/>
       <x:c r="J7" s="21"/>
       <x:c r="K7" s="30" t="s">
-        <x:v>6</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L7" s="31"/>
       <x:c r="M7" s="21"/>
     </x:row>
     <x:row r="8" spans="2:13" ht="25.5" customHeight="1">
       <x:c r="B8" s="6" t="s">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C8" s="7" t="s">
-        <x:v>4</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D8" s="8" t="s">
-        <x:v>10</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E8" s="6" t="s">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F8" s="7" t="s">
-        <x:v>4</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G8" s="8" t="s">
-        <x:v>10</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H8" s="6" t="s">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="I8" s="7" t="s">
-        <x:v>4</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="J8" s="8" t="s">
-        <x:v>10</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K8" s="6" t="s">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="L8" s="7" t="s">
-        <x:v>4</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="M8" s="8" t="s">
-        <x:v>10</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="2:13" ht="25.5" customHeight="1">
@@ -25702,7 +25711,7 @@
       <x:c r="B27" s="16" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C27" s="32">
+      <x:c r="C27" s="34">
         <x:f>SUM(D9:D26)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -25710,7 +25719,7 @@
       <x:c r="E27" s="16" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="F27" s="32">
+      <x:c r="F27" s="34">
         <x:f>SUM(G9:G26)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -25718,7 +25727,7 @@
       <x:c r="H27" s="16" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I27" s="32">
+      <x:c r="I27" s="34">
         <x:f>SUM(J9:J26)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -25726,7 +25735,7 @@
       <x:c r="K27" s="16" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="L27" s="32">
+      <x:c r="L27" s="34">
         <x:f>SUM(M9:M26)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -25745,9 +25754,9 @@
     <x:row r="29" spans="1:23" ht="25.5" customHeight="1">
       <x:c r="A29" s="17"/>
       <x:c r="B29" s="6" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C29" s="33">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C29" s="35">
         <x:f>SUM(C27:D27,F27:G27,I27:J27,L27:M27)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -28744,26 +28753,26 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="2:7" ht="25.5" customHeight="1">
-      <x:c r="B1" s="34"/>
+      <x:c r="B1" s="32"/>
       <x:c r="C1" s="21"/>
       <x:c r="D1" s="1"/>
       <x:c r="E1" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F1" s="20"/>
       <x:c r="G1" s="21"/>
     </x:row>
     <x:row r="2" spans="2:9" ht="25.5" customHeight="1">
       <x:c r="B2" s="22" t="s">
-        <x:v>3</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C2" s="24">
         <x:f>SUM(F1:G1,-C29:D29)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D2" s="25"/>
-      <x:c r="F2" s="35" t="s">
-        <x:v>15</x:v>
+      <x:c r="F2" s="33" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G2" s="31"/>
       <x:c r="H2" s="31"/>
@@ -28779,29 +28788,29 @@
     </x:row>
     <x:row r="5" spans="2:13" ht="25.5" customHeight="1">
       <x:c r="B5" s="2" t="s">
-        <x:v>13</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C5" s="28"/>
       <x:c r="D5" s="21"/>
       <x:c r="E5" s="3" t="s">
-        <x:v>13</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F5" s="28"/>
       <x:c r="G5" s="21"/>
       <x:c r="H5" s="3" t="s">
-        <x:v>13</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="I5" s="28"/>
       <x:c r="J5" s="21"/>
       <x:c r="K5" s="3" t="s">
-        <x:v>13</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="L5" s="28"/>
       <x:c r="M5" s="21"/>
     </x:row>
     <x:row r="6" spans="2:13" ht="25.5" customHeight="1">
       <x:c r="B6" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C6" s="29">
         <x:f>SUM(C5:D5,-C27:D27)</x:f>
@@ -28809,7 +28818,7 @@
       </x:c>
       <x:c r="D6" s="21"/>
       <x:c r="E6" s="5" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F6" s="29">
         <x:f>SUM(F5:G5,-F27:G27)</x:f>
@@ -28817,7 +28826,7 @@
       </x:c>
       <x:c r="G6" s="21"/>
       <x:c r="H6" s="5" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="I6" s="29">
         <x:f>SUM(I5:J5,-I27:J27)</x:f>
@@ -28825,7 +28834,7 @@
       </x:c>
       <x:c r="J6" s="21"/>
       <x:c r="K6" s="5" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="L6" s="29">
         <x:f>SUM(L5:M5,-L27:M27)</x:f>
@@ -28835,62 +28844,62 @@
     </x:row>
     <x:row r="7" spans="2:13" ht="25.5" customHeight="1">
       <x:c r="B7" s="30" t="s">
-        <x:v>11</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C7" s="31"/>
       <x:c r="D7" s="21"/>
       <x:c r="E7" s="30" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F7" s="31"/>
       <x:c r="G7" s="21"/>
       <x:c r="H7" s="30" t="s">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I7" s="31"/>
       <x:c r="J7" s="21"/>
       <x:c r="K7" s="30" t="s">
-        <x:v>6</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L7" s="31"/>
       <x:c r="M7" s="21"/>
     </x:row>
     <x:row r="8" spans="2:13" ht="25.5" customHeight="1">
       <x:c r="B8" s="6" t="s">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C8" s="7" t="s">
-        <x:v>4</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D8" s="8" t="s">
-        <x:v>10</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E8" s="6" t="s">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F8" s="7" t="s">
-        <x:v>4</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G8" s="8" t="s">
-        <x:v>10</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H8" s="6" t="s">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="I8" s="7" t="s">
-        <x:v>4</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="J8" s="8" t="s">
-        <x:v>10</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K8" s="6" t="s">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="L8" s="7" t="s">
-        <x:v>4</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="M8" s="8" t="s">
-        <x:v>10</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="2:13" ht="25.5" customHeight="1">
@@ -29150,7 +29159,7 @@
       <x:c r="B27" s="16" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C27" s="32">
+      <x:c r="C27" s="34">
         <x:f>SUM(D9:D26)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -29158,7 +29167,7 @@
       <x:c r="E27" s="16" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="F27" s="32">
+      <x:c r="F27" s="34">
         <x:f>SUM(G9:G26)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -29166,7 +29175,7 @@
       <x:c r="H27" s="16" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I27" s="32">
+      <x:c r="I27" s="34">
         <x:f>SUM(J9:J26)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -29174,7 +29183,7 @@
       <x:c r="K27" s="16" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="L27" s="32">
+      <x:c r="L27" s="34">
         <x:f>SUM(M9:M26)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -29193,9 +29202,9 @@
     <x:row r="29" spans="1:23" ht="25.5" customHeight="1">
       <x:c r="A29" s="17"/>
       <x:c r="B29" s="6" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C29" s="33">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C29" s="35">
         <x:f>SUM(C27:D27,F27:G27,I27:J27,L27:M27)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -32192,26 +32201,26 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="2:7" ht="25.5" customHeight="1">
-      <x:c r="B1" s="34"/>
+      <x:c r="B1" s="32"/>
       <x:c r="C1" s="21"/>
       <x:c r="D1" s="1"/>
       <x:c r="E1" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F1" s="20"/>
       <x:c r="G1" s="21"/>
     </x:row>
     <x:row r="2" spans="2:9" ht="25.5" customHeight="1">
       <x:c r="B2" s="22" t="s">
-        <x:v>3</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C2" s="24">
         <x:f>SUM(F1:G1,-C29:D29)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D2" s="25"/>
-      <x:c r="F2" s="35" t="s">
-        <x:v>15</x:v>
+      <x:c r="F2" s="33" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G2" s="31"/>
       <x:c r="H2" s="31"/>
@@ -32227,29 +32236,29 @@
     </x:row>
     <x:row r="5" spans="2:13" ht="25.5" customHeight="1">
       <x:c r="B5" s="2" t="s">
-        <x:v>13</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C5" s="28"/>
       <x:c r="D5" s="21"/>
       <x:c r="E5" s="3" t="s">
-        <x:v>13</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F5" s="28"/>
       <x:c r="G5" s="21"/>
       <x:c r="H5" s="3" t="s">
-        <x:v>13</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="I5" s="28"/>
       <x:c r="J5" s="21"/>
       <x:c r="K5" s="3" t="s">
-        <x:v>13</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="L5" s="28"/>
       <x:c r="M5" s="21"/>
     </x:row>
     <x:row r="6" spans="2:13" ht="25.5" customHeight="1">
       <x:c r="B6" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C6" s="29">
         <x:f>SUM(C5:D5,-C27:D27)</x:f>
@@ -32257,7 +32266,7 @@
       </x:c>
       <x:c r="D6" s="21"/>
       <x:c r="E6" s="5" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F6" s="29">
         <x:f>SUM(F5:G5,-F27:G27)</x:f>
@@ -32265,7 +32274,7 @@
       </x:c>
       <x:c r="G6" s="21"/>
       <x:c r="H6" s="5" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="I6" s="29">
         <x:f>SUM(I5:J5,-I27:J27)</x:f>
@@ -32273,7 +32282,7 @@
       </x:c>
       <x:c r="J6" s="21"/>
       <x:c r="K6" s="5" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="L6" s="29">
         <x:f>SUM(L5:M5,-L27:M27)</x:f>
@@ -32283,62 +32292,62 @@
     </x:row>
     <x:row r="7" spans="2:13" ht="25.5" customHeight="1">
       <x:c r="B7" s="30" t="s">
-        <x:v>11</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C7" s="31"/>
       <x:c r="D7" s="21"/>
       <x:c r="E7" s="30" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F7" s="31"/>
       <x:c r="G7" s="21"/>
       <x:c r="H7" s="30" t="s">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I7" s="31"/>
       <x:c r="J7" s="21"/>
       <x:c r="K7" s="30" t="s">
-        <x:v>6</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L7" s="31"/>
       <x:c r="M7" s="21"/>
     </x:row>
     <x:row r="8" spans="2:13" ht="25.5" customHeight="1">
       <x:c r="B8" s="6" t="s">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C8" s="7" t="s">
-        <x:v>4</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D8" s="8" t="s">
-        <x:v>10</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E8" s="6" t="s">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F8" s="7" t="s">
-        <x:v>4</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G8" s="8" t="s">
-        <x:v>10</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H8" s="6" t="s">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="I8" s="7" t="s">
-        <x:v>4</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="J8" s="8" t="s">
-        <x:v>10</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K8" s="6" t="s">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="L8" s="7" t="s">
-        <x:v>4</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="M8" s="8" t="s">
-        <x:v>10</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="2:13" ht="25.5" customHeight="1">
@@ -32598,7 +32607,7 @@
       <x:c r="B27" s="16" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C27" s="32">
+      <x:c r="C27" s="34">
         <x:f>SUM(D9:D26)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -32606,7 +32615,7 @@
       <x:c r="E27" s="16" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="F27" s="32">
+      <x:c r="F27" s="34">
         <x:f>SUM(G9:G26)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -32614,7 +32623,7 @@
       <x:c r="H27" s="16" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I27" s="32">
+      <x:c r="I27" s="34">
         <x:f>SUM(J9:J26)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -32622,7 +32631,7 @@
       <x:c r="K27" s="16" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="L27" s="32">
+      <x:c r="L27" s="34">
         <x:f>SUM(M9:M26)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -32641,9 +32650,9 @@
     <x:row r="29" spans="1:23" ht="25.5" customHeight="1">
       <x:c r="A29" s="17"/>
       <x:c r="B29" s="6" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C29" s="33">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C29" s="35">
         <x:f>SUM(C27:D27,F27:G27,I27:J27,L27:M27)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -35640,26 +35649,26 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="2:7" ht="25.5" customHeight="1">
-      <x:c r="B1" s="34"/>
+      <x:c r="B1" s="32"/>
       <x:c r="C1" s="21"/>
       <x:c r="D1" s="1"/>
       <x:c r="E1" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F1" s="20"/>
       <x:c r="G1" s="21"/>
     </x:row>
     <x:row r="2" spans="2:9" ht="25.5" customHeight="1">
       <x:c r="B2" s="22" t="s">
-        <x:v>3</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C2" s="24">
         <x:f>SUM(F1:G1,-C29:D29)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D2" s="25"/>
-      <x:c r="F2" s="35" t="s">
-        <x:v>15</x:v>
+      <x:c r="F2" s="33" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G2" s="31"/>
       <x:c r="H2" s="31"/>
@@ -35675,29 +35684,29 @@
     </x:row>
     <x:row r="5" spans="2:13" ht="25.5" customHeight="1">
       <x:c r="B5" s="2" t="s">
-        <x:v>13</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C5" s="28"/>
       <x:c r="D5" s="21"/>
       <x:c r="E5" s="3" t="s">
-        <x:v>13</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F5" s="28"/>
       <x:c r="G5" s="21"/>
       <x:c r="H5" s="3" t="s">
-        <x:v>13</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="I5" s="28"/>
       <x:c r="J5" s="21"/>
       <x:c r="K5" s="3" t="s">
-        <x:v>13</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="L5" s="28"/>
       <x:c r="M5" s="21"/>
     </x:row>
     <x:row r="6" spans="2:13" ht="25.5" customHeight="1">
       <x:c r="B6" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C6" s="29">
         <x:f>SUM(C5:D5,-C27:D27)</x:f>
@@ -35705,7 +35714,7 @@
       </x:c>
       <x:c r="D6" s="21"/>
       <x:c r="E6" s="5" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F6" s="29">
         <x:f>SUM(F5:G5,-F27:G27)</x:f>
@@ -35713,7 +35722,7 @@
       </x:c>
       <x:c r="G6" s="21"/>
       <x:c r="H6" s="5" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="I6" s="29">
         <x:f>SUM(I5:J5,-I27:J27)</x:f>
@@ -35721,7 +35730,7 @@
       </x:c>
       <x:c r="J6" s="21"/>
       <x:c r="K6" s="5" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="L6" s="29">
         <x:f>SUM(L5:M5,-L27:M27)</x:f>
@@ -35731,62 +35740,62 @@
     </x:row>
     <x:row r="7" spans="2:13" ht="25.5" customHeight="1">
       <x:c r="B7" s="30" t="s">
-        <x:v>11</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C7" s="31"/>
       <x:c r="D7" s="21"/>
       <x:c r="E7" s="30" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F7" s="31"/>
       <x:c r="G7" s="21"/>
       <x:c r="H7" s="30" t="s">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I7" s="31"/>
       <x:c r="J7" s="21"/>
       <x:c r="K7" s="30" t="s">
-        <x:v>6</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L7" s="31"/>
       <x:c r="M7" s="21"/>
     </x:row>
     <x:row r="8" spans="2:13" ht="25.5" customHeight="1">
       <x:c r="B8" s="6" t="s">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C8" s="7" t="s">
-        <x:v>4</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D8" s="8" t="s">
-        <x:v>10</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E8" s="6" t="s">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F8" s="7" t="s">
-        <x:v>4</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G8" s="8" t="s">
-        <x:v>10</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H8" s="6" t="s">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="I8" s="7" t="s">
-        <x:v>4</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="J8" s="8" t="s">
-        <x:v>10</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K8" s="6" t="s">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="L8" s="7" t="s">
-        <x:v>4</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="M8" s="8" t="s">
-        <x:v>10</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="2:13" ht="25.5" customHeight="1">
@@ -36046,7 +36055,7 @@
       <x:c r="B27" s="16" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C27" s="32">
+      <x:c r="C27" s="34">
         <x:f>SUM(D9:D26)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -36054,7 +36063,7 @@
       <x:c r="E27" s="16" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="F27" s="32">
+      <x:c r="F27" s="34">
         <x:f>SUM(G9:G26)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -36062,7 +36071,7 @@
       <x:c r="H27" s="16" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I27" s="32">
+      <x:c r="I27" s="34">
         <x:f>SUM(J9:J26)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -36070,7 +36079,7 @@
       <x:c r="K27" s="16" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="L27" s="32">
+      <x:c r="L27" s="34">
         <x:f>SUM(M9:M26)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -36089,9 +36098,9 @@
     <x:row r="29" spans="1:23" ht="25.5" customHeight="1">
       <x:c r="A29" s="17"/>
       <x:c r="B29" s="6" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C29" s="33">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C29" s="35">
         <x:f>SUM(C27:D27,F27:G27,I27:J27,L27:M27)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -39088,26 +39097,26 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="2:7" ht="25.5" customHeight="1">
-      <x:c r="B1" s="34"/>
+      <x:c r="B1" s="32"/>
       <x:c r="C1" s="21"/>
       <x:c r="D1" s="1"/>
       <x:c r="E1" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F1" s="20"/>
       <x:c r="G1" s="21"/>
     </x:row>
     <x:row r="2" spans="2:9" ht="25.5" customHeight="1">
       <x:c r="B2" s="22" t="s">
-        <x:v>3</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C2" s="24">
         <x:f>SUM(F1:G1,-C29:D29)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D2" s="25"/>
-      <x:c r="F2" s="35" t="s">
-        <x:v>15</x:v>
+      <x:c r="F2" s="33" t="s">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G2" s="31"/>
       <x:c r="H2" s="31"/>
@@ -39123,29 +39132,29 @@
     </x:row>
     <x:row r="5" spans="2:13" ht="25.5" customHeight="1">
       <x:c r="B5" s="2" t="s">
-        <x:v>13</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C5" s="28"/>
       <x:c r="D5" s="21"/>
       <x:c r="E5" s="3" t="s">
-        <x:v>13</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F5" s="28"/>
       <x:c r="G5" s="21"/>
       <x:c r="H5" s="3" t="s">
-        <x:v>13</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="I5" s="28"/>
       <x:c r="J5" s="21"/>
       <x:c r="K5" s="3" t="s">
-        <x:v>13</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="L5" s="28"/>
       <x:c r="M5" s="21"/>
     </x:row>
     <x:row r="6" spans="2:13" ht="25.5" customHeight="1">
       <x:c r="B6" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C6" s="29">
         <x:f>SUM(C5:D5,-C27:D27)</x:f>
@@ -39153,7 +39162,7 @@
       </x:c>
       <x:c r="D6" s="21"/>
       <x:c r="E6" s="5" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F6" s="29">
         <x:f>SUM(F5:G5,-F27:G27)</x:f>
@@ -39161,7 +39170,7 @@
       </x:c>
       <x:c r="G6" s="21"/>
       <x:c r="H6" s="5" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="I6" s="29">
         <x:f>SUM(I5:J5,-I27:J27)</x:f>
@@ -39169,7 +39178,7 @@
       </x:c>
       <x:c r="J6" s="21"/>
       <x:c r="K6" s="5" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="L6" s="29">
         <x:f>SUM(L5:M5,-L27:M27)</x:f>
@@ -39179,62 +39188,62 @@
     </x:row>
     <x:row r="7" spans="2:13" ht="25.5" customHeight="1">
       <x:c r="B7" s="30" t="s">
-        <x:v>11</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C7" s="31"/>
       <x:c r="D7" s="21"/>
       <x:c r="E7" s="30" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F7" s="31"/>
       <x:c r="G7" s="21"/>
       <x:c r="H7" s="30" t="s">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I7" s="31"/>
       <x:c r="J7" s="21"/>
       <x:c r="K7" s="30" t="s">
-        <x:v>6</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L7" s="31"/>
       <x:c r="M7" s="21"/>
     </x:row>
     <x:row r="8" spans="2:13" ht="25.5" customHeight="1">
       <x:c r="B8" s="6" t="s">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C8" s="7" t="s">
-        <x:v>4</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D8" s="8" t="s">
-        <x:v>10</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E8" s="6" t="s">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F8" s="7" t="s">
-        <x:v>4</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G8" s="8" t="s">
-        <x:v>10</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H8" s="6" t="s">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="I8" s="7" t="s">
-        <x:v>4</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="J8" s="8" t="s">
-        <x:v>10</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K8" s="6" t="s">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="L8" s="7" t="s">
-        <x:v>4</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="M8" s="8" t="s">
-        <x:v>10</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="2:13" ht="25.5" customHeight="1">
@@ -39494,7 +39503,7 @@
       <x:c r="B27" s="16" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C27" s="32">
+      <x:c r="C27" s="34">
         <x:f>SUM(D9:D26)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -39502,7 +39511,7 @@
       <x:c r="E27" s="16" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="F27" s="32">
+      <x:c r="F27" s="34">
         <x:f>SUM(G9:G26)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -39510,7 +39519,7 @@
       <x:c r="H27" s="16" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I27" s="32">
+      <x:c r="I27" s="34">
         <x:f>SUM(J9:J26)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -39518,7 +39527,7 @@
       <x:c r="K27" s="16" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="L27" s="32">
+      <x:c r="L27" s="34">
         <x:f>SUM(M9:M26)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -39537,9 +39546,9 @@
     <x:row r="29" spans="1:23" ht="25.5" customHeight="1">
       <x:c r="A29" s="17"/>
       <x:c r="B29" s="6" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C29" s="33">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C29" s="35">
         <x:f>SUM(C27:D27,F27:G27,I27:J27,L27:M27)</x:f>
         <x:v>0</x:v>
       </x:c>
